--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050, 2000, 8010</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050, 2000, 8010</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
     </row>
@@ -16013,54 +16013,54 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 제조업</t>
+          <t xml:space="preserve">바이오비료 제조업</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 제조</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 제조업</t>
+          <t xml:space="preserve">바이오사료 제조업</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -16070,61 +16070,61 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">보조사료·사료첨가제 제조분; 단미사료 제외</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 제조업</t>
+          <t xml:space="preserve">바이오사료 제조업</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 제조</t>
+          <t xml:space="preserve">첨가제 외 바이오사료 제조분</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 제조업</t>
+          <t xml:space="preserve">바이오사료 제조업</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -16134,29 +16134,29 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">229</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -16166,29 +16166,29 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">생분해성 농업용 필름·용기</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">229</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -16198,29 +16198,29 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">보조사료·사료첨가제 제조분; 단미사료 제외</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">229</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -16230,61 +16230,61 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료 제조분</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">231</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
+          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">생명공학 기반 식품첨가물 제조</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">231</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -16294,51 +16294,51 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 필름·용기</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재</t>
+          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -16365,22 +16365,22 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -16390,19 +16390,19 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 기반 식품첨가물 제조</t>
+          <t xml:space="preserve">법정 건강기능식품 제조</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -16429,44 +16429,44 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -16493,44 +16493,44 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정 건강기능식품 제조</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -16557,12 +16557,12 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -16582,19 +16582,19 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -16621,44 +16621,44 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -16685,44 +16685,44 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
+          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -16749,54 +16749,54 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -16806,51 +16806,51 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오고분자 생활소재</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -16877,22 +16877,22 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,29 +16902,29 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 산업용 제품</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -16934,29 +16934,29 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -16966,19 +16966,19 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -17005,86 +17005,86 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
+          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
+          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -17094,93 +17094,93 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -17190,19 +17190,19 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -17229,22 +17229,22 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -17254,157 +17254,157 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -17414,19 +17414,19 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -17453,22 +17453,22 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17478,19 +17478,19 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -17517,22 +17517,22 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -17542,19 +17542,19 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -17574,29 +17574,29 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,19 +17606,19 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -17645,22 +17645,22 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17670,19 +17670,19 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -17702,29 +17702,29 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17734,19 +17734,19 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -17766,125 +17766,125 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17894,115 +17894,115 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -18029,12 +18029,12 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -18049,24 +18049,24 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -18093,22 +18093,22 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -18118,29 +18118,29 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,29 +18150,29 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,93 +18182,93 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,29 +18278,29 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,61 +18310,61 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,29 +18374,29 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,29 +18406,29 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,29 +18438,29 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,29 +18470,29 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,29 +18502,29 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,29 +18534,29 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,19 +18566,19 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -18605,54 +18605,54 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,61 +18662,61 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,61 +18726,61 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,61 +18790,61 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,19 +18854,19 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -18893,12 +18893,12 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -18918,19 +18918,19 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -18957,54 +18957,54 @@
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -19014,29 +19014,29 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -19046,93 +19046,93 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -19142,93 +19142,93 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -19238,29 +19238,29 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -19270,51 +19270,51 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
@@ -19341,22 +19341,22 @@
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -19366,29 +19366,29 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -19398,29 +19398,29 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -19430,19 +19430,19 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
@@ -19469,22 +19469,22 @@
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -19494,29 +19494,29 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,29 +19526,29 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,29 +19558,29 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -19590,29 +19590,29 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -19622,29 +19622,29 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -19654,29 +19654,29 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -19686,29 +19686,29 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -19718,29 +19718,29 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -19750,29 +19750,29 @@
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -19782,29 +19782,29 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -19814,29 +19814,29 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -19846,29 +19846,29 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -19878,29 +19878,29 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -19910,29 +19910,29 @@
       </c>
       <c r="F150" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -19942,29 +19942,29 @@
       </c>
       <c r="F151" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -19973,134 +19973,6 @@
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D153" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F153" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8030</t>
-        </is>
-      </c>
-      <c r="D154" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F154" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B155" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D155" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F155" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D156" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F156" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -947,7 +947,7 @@
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050, 3000, 8010</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
     </row>
@@ -16077,22 +16077,22 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">229</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -16102,29 +16102,29 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료 제조분</t>
+          <t xml:space="preserve">생분해성 농업용 필름·용기</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">229</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재</t>
         </is>
       </c>
     </row>
@@ -16151,12 +16151,12 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -16166,51 +16166,51 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 필름·용기</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">231</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재</t>
+          <t xml:space="preserve">생명공학 기반 식품첨가물 제조</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">231</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -16237,22 +16237,22 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -16262,19 +16262,19 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 기반 식품첨가물 제조</t>
+          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -16301,22 +16301,22 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -16326,19 +16326,19 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
+          <t xml:space="preserve">법정 건강기능식품 제조</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -16365,44 +16365,44 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정 건강기능식품 제조</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -16429,12 +16429,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -16454,19 +16454,19 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -16493,12 +16493,12 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -16518,19 +16518,19 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -16557,44 +16557,44 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
+          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -16621,22 +16621,22 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -16646,19 +16646,19 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
+          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -16685,12 +16685,12 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -16705,34 +16705,34 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오고분자 생활소재</t>
         </is>
       </c>
     </row>
@@ -16759,12 +16759,12 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -16791,12 +16791,12 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -16806,29 +16806,29 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -16838,29 +16838,29 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">바이오고분자 산업용 제품</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
         </is>
       </c>
     </row>
@@ -16887,12 +16887,12 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
+          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
         </is>
       </c>
     </row>
@@ -16919,12 +16919,12 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -16934,71 +16934,71 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
+          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17015,44 +17015,44 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -17062,19 +17062,19 @@
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -17101,12 +17101,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -17126,19 +17126,19 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -17165,22 +17165,22 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -17190,39 +17190,39 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17239,44 +17239,44 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -17286,19 +17286,19 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -17325,22 +17325,22 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -17350,19 +17350,19 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -17389,12 +17389,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -17414,19 +17414,19 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -17453,22 +17453,22 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17478,19 +17478,19 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -17510,19 +17510,19 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -17549,12 +17549,12 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -17574,29 +17574,29 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,19 +17606,19 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -17638,19 +17638,19 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -17670,19 +17670,19 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
+          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -17702,93 +17702,93 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
+          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
@@ -17815,66 +17815,66 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -17901,12 +17901,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -17926,19 +17926,19 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -17965,12 +17965,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -17985,24 +17985,24 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -18029,54 +18029,54 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
@@ -18103,76 +18103,76 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
@@ -18199,44 +18199,44 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,29 +18246,29 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,29 +18310,29 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,29 +18342,29 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
@@ -18391,12 +18391,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,29 +18406,29 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,29 +18438,29 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,51 +18534,51 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -18605,22 +18605,22 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
@@ -18679,44 +18679,44 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,19 +18726,19 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -18765,12 +18765,12 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -18790,19 +18790,19 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -18829,12 +18829,12 @@
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -18854,19 +18854,19 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -18893,54 +18893,54 @@
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18967,76 +18967,76 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -19063,66 +19063,66 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -19142,19 +19142,19 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -19169,34 +19169,34 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -19223,12 +19223,12 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -19238,7 +19238,7 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -19255,12 +19255,12 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -19270,29 +19270,29 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -19302,29 +19302,29 @@
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19351,12 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -19383,12 +19383,12 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -19398,29 +19398,29 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -19430,29 +19430,29 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -19462,19 +19462,19 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -19494,29 +19494,29 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,29 +19526,29 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,19 +19558,19 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
@@ -19590,19 +19590,19 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -19622,29 +19622,29 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -19654,29 +19654,29 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
@@ -19703,12 +19703,12 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -19718,29 +19718,29 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
+          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -19750,29 +19750,29 @@
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -19782,29 +19782,29 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -19814,29 +19814,29 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -19863,12 +19863,12 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -19895,12 +19895,12 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -19909,70 +19909,6 @@
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B151" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D151" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F151" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D152" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F152" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030, 8010</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
     </row>
@@ -16205,32 +16205,32 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
         </is>
       </c>
     </row>
@@ -16247,54 +16247,54 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">법정 건강기능식품 제조</t>
         </is>
       </c>
     </row>
@@ -16311,44 +16311,44 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정 건강기능식품 제조</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
@@ -16375,12 +16375,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -16390,29 +16390,29 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
@@ -16439,12 +16439,12 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -16454,29 +16454,29 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16503,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -16518,39 +16518,39 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
         </is>
       </c>
     </row>
@@ -16567,54 +16567,54 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
         </is>
       </c>
     </row>
@@ -16631,44 +16631,44 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -16695,12 +16695,12 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 생활소재</t>
         </is>
       </c>
     </row>
@@ -16727,12 +16727,12 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -16759,12 +16759,12 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -16774,29 +16774,29 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -16806,7 +16806,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오고분자 산업용 제품</t>
         </is>
       </c>
     </row>
@@ -16823,12 +16823,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
         </is>
       </c>
     </row>
@@ -16855,12 +16855,12 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
+          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
         </is>
       </c>
     </row>
@@ -16887,12 +16887,12 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,39 +16902,39 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -16951,12 +16951,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -16983,54 +16983,54 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17047,54 +17047,54 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17111,54 +17111,54 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17175,12 +17175,12 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17207,54 +17207,54 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
@@ -17271,54 +17271,54 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17335,54 +17335,54 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
         </is>
       </c>
     </row>
@@ -17399,54 +17399,54 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
@@ -17463,54 +17463,54 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
@@ -17527,54 +17527,54 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
@@ -17591,54 +17591,54 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
+          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
         </is>
       </c>
     </row>
@@ -17655,34 +17655,34 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -17702,39 +17702,39 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
+          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
@@ -17751,22 +17751,22 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
@@ -17783,12 +17783,12 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17798,39 +17798,39 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
@@ -17847,54 +17847,54 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
@@ -17911,44 +17911,44 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
@@ -17975,12 +17975,12 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,39 +17990,39 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
@@ -18039,22 +18039,22 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
@@ -18071,12 +18071,12 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -18086,39 +18086,39 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
@@ -18135,22 +18135,22 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
@@ -18167,12 +18167,12 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,29 +18182,29 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
@@ -18231,12 +18231,12 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
@@ -18263,12 +18263,12 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,29 +18278,29 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
@@ -18327,12 +18327,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
@@ -18359,12 +18359,12 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,29 +18374,29 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18423,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,39 +18502,39 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
@@ -18551,54 +18551,54 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
@@ -18615,22 +18615,22 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
@@ -18647,12 +18647,12 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,29 +18662,29 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18775,12 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,29 +18790,29 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
@@ -18839,12 +18839,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,39 +18854,39 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
@@ -18903,22 +18903,22 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18935,12 +18935,12 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18950,39 +18950,39 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
@@ -18999,22 +18999,22 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -19031,12 +19031,12 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -19046,39 +19046,39 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
@@ -19095,44 +19095,44 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -19159,12 +19159,12 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -19191,12 +19191,12 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -19223,12 +19223,12 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -19238,29 +19238,29 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -19270,7 +19270,7 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
@@ -19287,12 +19287,12 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -19319,12 +19319,12 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19351,12 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -19366,19 +19366,19 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
@@ -19415,12 +19415,12 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -19430,29 +19430,29 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -19462,29 +19462,29 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,29 +19526,29 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -19590,29 +19590,29 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
         </is>
       </c>
     </row>
@@ -19639,12 +19639,12 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
@@ -19671,12 +19671,12 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -19686,19 +19686,19 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
+          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
         </is>
       </c>
     </row>
@@ -19735,12 +19735,12 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -19750,29 +19750,29 @@
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -19799,12 +19799,12 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -19831,12 +19831,12 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -19863,12 +19863,12 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -19877,38 +19877,6 @@
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D150" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F150" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -1118,7 +1118,7 @@
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040, 8010</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010, 8010</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000, 8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000, 8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000, 8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
     </row>
@@ -16237,86 +16237,86 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">233</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">법정 건강기능식품 제조</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">234</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">법정 건강기능식품 제조</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">235</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -16326,19 +16326,19 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -16358,61 +16358,61 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">234</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -16422,61 +16422,61 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">235</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -16486,29 +16486,29 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -16518,61 +16518,61 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
+          <t xml:space="preserve">바이오고분자 생활소재</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -16582,61 +16582,61 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -16646,29 +16646,29 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오고분자 산업용 제품</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -16678,29 +16678,29 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -16710,29 +16710,29 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
+          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8010</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -16742,93 +16742,93 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
+          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -16838,61 +16838,61 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,29 +16902,29 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -16934,93 +16934,93 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -17030,19 +17030,19 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -17069,22 +17069,22 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -17094,19 +17094,19 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -17133,22 +17133,22 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -17158,371 +17158,371 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
+          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
+          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -17542,61 +17542,61 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,93 +17606,93 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -17702,29 +17702,29 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17734,29 +17734,29 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -17766,29 +17766,29 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17798,115 +17798,115 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -17933,54 +17933,54 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,61 +17990,61 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -18054,29 +18054,29 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -18086,61 +18086,61 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,29 +18150,29 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,29 +18182,29 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18214,29 +18214,29 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,29 +18246,29 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,29 +18278,29 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,29 +18310,29 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,61 +18342,61 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,61 +18406,61 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,19 +18470,19 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -18509,44 +18509,44 @@
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -18573,54 +18573,54 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,29 +18662,29 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,61 +18694,61 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,19 +18758,19 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -18790,61 +18790,61 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,83 +18854,83 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -18950,61 +18950,61 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -19014,29 +19014,29 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -19046,61 +19046,61 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -19110,29 +19110,29 @@
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -19142,29 +19142,29 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -19174,29 +19174,29 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -19206,19 +19206,19 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -19238,29 +19238,29 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -19270,29 +19270,29 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -19302,29 +19302,29 @@
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -19334,29 +19334,29 @@
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -19366,29 +19366,29 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -19398,19 +19398,19 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
@@ -19430,29 +19430,29 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -19462,29 +19462,29 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -19494,29 +19494,29 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,29 +19526,29 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,29 +19558,29 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -19590,29 +19590,29 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -19622,29 +19622,29 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -19654,29 +19654,29 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -19686,29 +19686,29 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -19717,166 +19717,6 @@
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B147" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8030</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F147" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B148" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F148" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F149" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3626,7 +3626,7 @@
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030, 4010, 4000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
     </row>
@@ -19447,12 +19447,12 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -19462,29 +19462,29 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 폐자원 처리·재활용 제제 또는 시스템 제공분</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -19494,29 +19494,29 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,29 +19526,29 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오환경 서비스; 독립 처리수수료 사업 전체를 직접 포괄하지 않음</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,29 +19558,29 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -19607,12 +19607,12 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -19639,12 +19639,12 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -19653,70 +19653,6 @@
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B143" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3683,7 +3683,7 @@
       </c>
       <c r="K63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000, 4010</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
     </row>
@@ -19479,12 +19479,12 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -19494,29 +19494,29 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물학적 농업환경 관리·개선 서비스가 잔여 바이오환경 범위에 들 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -19543,12 +19543,12 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -19575,12 +19575,12 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -19607,12 +19607,12 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -19621,38 +19621,6 @@
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F142" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -1629,11 +1629,7 @@
           <t xml:space="preserve">13116, 42230, 42920</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7010, 7000, 8050</t>
-        </is>
-      </c>
+      <c r="K27" s="10"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1686,11 +1682,7 @@
           <t xml:space="preserve">13113</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050, 8050</t>
-        </is>
-      </c>
+      <c r="K28" s="10"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1743,11 +1735,7 @@
           <t xml:space="preserve">13112</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050, 8050</t>
-        </is>
-      </c>
+      <c r="K29" s="10"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1800,11 +1788,7 @@
           <t xml:space="preserve">13114</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3050, 3000, 8050</t>
-        </is>
-      </c>
+      <c r="K30" s="10"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1857,11 +1841,7 @@
           <t xml:space="preserve">13119, 13210</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000, 8050</t>
-        </is>
-      </c>
+      <c r="K31" s="10"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1914,11 +1894,7 @@
           <t xml:space="preserve">42363, 43229</t>
         </is>
       </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010, 8050</t>
-        </is>
-      </c>
+      <c r="K32" s="10"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1971,11 +1947,7 @@
           <t xml:space="preserve">43229</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010, 8050</t>
-        </is>
-      </c>
+      <c r="K33" s="10"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2028,11 +2000,7 @@
           <t xml:space="preserve">42390</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 8050</t>
-        </is>
-      </c>
+      <c r="K34" s="10"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2085,11 +2053,7 @@
           <t xml:space="preserve">42390, 43290</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 8050</t>
-        </is>
-      </c>
+      <c r="K35" s="10"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2142,11 +2106,7 @@
           <t xml:space="preserve">13115</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120, 8050</t>
-        </is>
-      </c>
+      <c r="K36" s="10"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2199,11 +2159,7 @@
           <t xml:space="preserve">13115</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120, 8050</t>
-        </is>
-      </c>
+      <c r="K37" s="10"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2256,11 +2212,7 @@
           <t xml:space="preserve">42920</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
+      <c r="K38" s="10"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -16749,12 +16701,12 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -16769,66 +16721,66 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 종자·묘목일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생물자원 취급품목 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -16838,61 +16790,61 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,61 +16854,61 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -16966,115 +16918,115 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목이 사료첨가제일 때의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제 외 바이오사료의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -17089,34 +17041,34 @@
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화학 농자재 취급품목 분야; 품목에 따라 재판정</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -17126,61 +17078,61 @@
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 판매업 자체의 대응 아님</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -17190,61 +17142,61 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야; 맞춤형 판매방식 전용 코드 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -17254,19 +17206,19 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -17281,34 +17233,34 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -17318,61 +17270,61 @@
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 위탁제조 판매만으로 8010 아님</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급 식품의 잔여 제품 분야; 실제 품목이 3010·3030·3040이면 해당 코드 재판정</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -17382,61 +17334,61 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 보관·배송 서비스 수행분; 단순 재판매·부수 배송 제외</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야; 도매업 자체의 대응 아님</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -17446,61 +17398,61 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표 위탁제조 동물용 의약품의 제품 분야; 판매형태 전용 코드 없음</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -17510,29 +17462,29 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 전문 의약품 보관·배송 서비스 수행분; 제조를 맡기는 발주자는 8010 아님</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -17542,29 +17494,29 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 생물류 처리·보관·배송 서비스 수행분만 대응; 판매품목 확인 전 제품 코드 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -17574,29 +17526,29 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,83 +17558,83 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -17709,44 +17661,44 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -17773,22 +17725,22 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17798,19 +17750,19 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -17837,54 +17789,54 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17894,93 +17846,93 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,61 +17942,61 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -18054,29 +18006,29 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -18086,61 +18038,61 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,29 +18102,29 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,29 +18134,29 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18214,29 +18166,29 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,29 +18198,29 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,29 +18230,29 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,29 +18262,29 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,51 +18294,51 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -18413,54 +18365,54 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,19 +18422,19 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -18502,29 +18454,29 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,29 +18486,29 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,29 +18518,29 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,29 +18550,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18582,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,29 +18614,29 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,51 +18646,51 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -18758,29 +18710,29 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,837 +18742,37 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8030</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4030</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
-        </is>
-      </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4000</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D130" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F130" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D132" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F132" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B134" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D134" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F134" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">531</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
-        </is>
-      </c>
-      <c r="E136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8030</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F139" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F140" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D141" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F141" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -1629,7 +1629,11 @@
           <t xml:space="preserve">13116, 42230, 42920</t>
         </is>
       </c>
-      <c r="K27" s="10"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7000</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1682,7 +1686,11 @@
           <t xml:space="preserve">13113</t>
         </is>
       </c>
-      <c r="K28" s="10"/>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2050</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1735,7 +1743,11 @@
           <t xml:space="preserve">13112</t>
         </is>
       </c>
-      <c r="K29" s="10"/>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2050</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1788,7 +1800,11 @@
           <t xml:space="preserve">13114</t>
         </is>
       </c>
-      <c r="K30" s="10"/>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3050</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1841,7 +1857,11 @@
           <t xml:space="preserve">13119, 13210</t>
         </is>
       </c>
-      <c r="K31" s="10"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1894,7 +1914,11 @@
           <t xml:space="preserve">42363, 43229</t>
         </is>
       </c>
-      <c r="K32" s="10"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3010</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1947,7 +1971,11 @@
           <t xml:space="preserve">43229</t>
         </is>
       </c>
-      <c r="K33" s="10"/>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3010</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2000,7 +2028,11 @@
           <t xml:space="preserve">42390</t>
         </is>
       </c>
-      <c r="K34" s="10"/>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3000</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2053,7 +2085,11 @@
           <t xml:space="preserve">42390, 43290</t>
         </is>
       </c>
-      <c r="K35" s="10"/>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3000</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2106,7 +2142,11 @@
           <t xml:space="preserve">13115</t>
         </is>
       </c>
-      <c r="K36" s="10"/>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2159,7 +2199,11 @@
           <t xml:space="preserve">13115</t>
         </is>
       </c>
-      <c r="K37" s="10"/>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2212,7 +2256,11 @@
           <t xml:space="preserve">42920</t>
         </is>
       </c>
-      <c r="K38" s="10"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2040</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -16701,406 +16749,406 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">생물자원 취급분의 대표 분야; 가공 소재는 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">사료첨가제 취급분의 제품 분야; 단미사료 등은 이 코드에 해당하지 않음</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">취급품목인 맞춤형 건강기능식품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 식품첨가물 등은 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">자기 상표로 판매하는 동물용 바이오의약품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">향장제품·생활제품 취급분의 대표 분야; 동물약국 등 다른 품목은 실제 제품에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -17110,29 +17158,29 @@
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -17142,19 +17190,19 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -17181,54 +17229,54 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -17238,61 +17286,61 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -17302,29 +17350,29 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -17334,19 +17382,19 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -17373,54 +17421,54 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17430,29 +17478,29 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -17462,83 +17510,83 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -17565,54 +17613,54 @@
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17622,19 +17670,19 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -17661,22 +17709,22 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17686,29 +17734,29 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -17718,29 +17766,29 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17750,29 +17798,29 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -17782,29 +17830,29 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17814,29 +17862,29 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17846,83 +17894,83 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -17942,29 +17990,29 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -17974,29 +18022,29 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -18006,19 +18054,19 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -18038,51 +18086,51 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -18109,22 +18157,22 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18134,29 +18182,29 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18166,29 +18214,29 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18198,19 +18246,19 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -18237,54 +18285,54 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18294,29 +18342,29 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18326,61 +18374,61 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18390,29 +18438,29 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18422,61 +18470,61 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18486,29 +18534,29 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18518,29 +18566,29 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18550,29 +18598,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18582,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18614,19 +18662,19 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -18646,29 +18694,29 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">590</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18678,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">590</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18710,29 +18758,29 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">590</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18742,37 +18790,421 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">462</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8040</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">462</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8000</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 바이오서비스업</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8040</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8020</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8000</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 바이오서비스업</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">529</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8020</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">529</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8000</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 바이오서비스업</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">531</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4010</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4010</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">590</t>
         </is>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8020</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8030</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8050</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8000</t>
         </is>
       </c>
-      <c r="D116" s="10" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조건부</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120, 8010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040, 8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040, 2010, 2000, 8010</t>
+          <t xml:space="preserve">2040, 2010, 2000</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010, 2000, 4000, 8010</t>
+          <t xml:space="preserve">2010, 2000, 4000</t>
         </is>
       </c>
     </row>
@@ -16397,44 +16397,44 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -16449,34 +16449,34 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">292</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오고분자 생활소재</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16503,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -16518,19 +16518,19 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -16550,19 +16550,19 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
+          <t xml:space="preserve">바이오고분자 산업용 제품</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -16582,29 +16582,29 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">292</t>
+          <t xml:space="preserve">299</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
+          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -16614,157 +16614,157 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
+          <t xml:space="preserve">생물자원 취급분의 대표 분야; 가공 소재는 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
+          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
+          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
+          <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8010</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">참고</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
+          <t xml:space="preserve">사료첨가제 취급분의 제품 분야; 단미사료 등은 이 코드에 해당하지 않음</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -16774,29 +16774,29 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물자원 취급분의 대표 분야; 가공 소재는 실제 품목에 따라 재판정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 판매업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -16806,29 +16806,29 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야</t>
+          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 판매업</t>
+          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -16838,29 +16838,29 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야</t>
+          <t xml:space="preserve">취급품목인 맞춤형 건강기능식품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 판매업</t>
+          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -16870,29 +16870,29 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 취급분의 제품 분야; 단미사료 등은 이 코드에 해당하지 않음</t>
+          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 식품첨가물 등은 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">329</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -16902,29 +16902,29 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
+          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -16934,29 +16934,29 @@
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야</t>
+          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -16966,29 +16966,29 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 맞춤형 건강기능식품의 제품 분야</t>
+          <t xml:space="preserve">자기 상표로 판매하는 동물용 바이오의약품의 제품 분야</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">390</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
+          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -16998,211 +16998,211 @@
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 식품첨가물 등은 실제 품목에 따라 재판정</t>
+          <t xml:space="preserve">향장제품·생활제품 취급분의 대표 분야; 동물약국 등 다른 품목은 실제 제품에 따라 재판정</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">7010</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
+          <t xml:space="preserve">종자·묘목 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">7020</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야</t>
+          <t xml:space="preserve">유전자변형 생물체 개발분</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
+          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">자기 상표로 판매하는 동물용 바이오의약품의 제품 분야</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">향장제품·생활제품 취급분의 대표 분야; 동물약국 등 다른 품목은 실제 제품에 따라 재판정</t>
+          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">412</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자 및 묘목</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7020</t>
+          <t xml:space="preserve">7000</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자 변형 생물체</t>
+          <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
+          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
+          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -17229,12 +17229,12 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -17249,24 +17249,24 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">412</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -17293,22 +17293,22 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -17318,29 +17318,29 @@
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
+          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -17350,29 +17350,29 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오자원</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -17382,93 +17382,93 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
+          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17478,29 +17478,29 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -17510,61 +17510,61 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -17574,29 +17574,29 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,29 +17606,29 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -17638,29 +17638,29 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17670,29 +17670,29 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -17702,29 +17702,29 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17734,29 +17734,29 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -17766,19 +17766,19 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -17805,54 +17805,54 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17862,61 +17862,61 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -17926,61 +17926,61 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,61 +17990,61 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -18054,19 +18054,19 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -18093,12 +18093,12 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -18118,19 +18118,19 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -18157,54 +18157,54 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18214,29 +18214,29 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,93 +18246,93 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,93 +18342,93 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,29 +18438,29 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,51 +18470,51 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -18541,22 +18541,22 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,29 +18566,29 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,29 +18598,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,19 +18630,19 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -18669,22 +18669,22 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,29 +18694,29 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,29 +18758,29 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,29 +18790,29 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18822,29 +18822,29 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,29 +18854,29 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18886,29 +18886,29 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -18918,29 +18918,29 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18950,19 +18950,19 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -18982,29 +18982,29 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -19014,29 +19014,29 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -19046,29 +19046,29 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -19077,134 +19077,6 @@
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F125" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8030</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
-        </is>
-      </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D128" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F128" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -2258,7 +2258,7 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
     </row>
@@ -16983,22 +16983,22 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">참고</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">향장제품·생활제품 취급분의 대표 분야; 동물약국 등 다른 품목은 실제 제품에 따라 재판정</t>
+          <t xml:space="preserve">그린바이오제품의 별도 가공·처리·보관 서비스를 수행하는 경우에 한정; 판매 자체는 제외</t>
         </is>
       </c>
     </row>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050, 2000, 8040</t>
+          <t xml:space="preserve">2050, 8040</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050, 2000, 8040</t>
+          <t xml:space="preserve">2050, 8040</t>
         </is>
       </c>
     </row>
@@ -17335,12 +17335,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -17350,39 +17350,39 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 농약이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
+          <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2050</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
         </is>
       </c>
     </row>
@@ -17399,44 +17399,44 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오농약 및 비료</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3050</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -17446,29 +17446,29 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생물공정 비료이나 생물학적 제제가 아닌 산출물</t>
+          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">423</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
+          <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
         </is>
       </c>
     </row>
@@ -17495,12 +17495,12 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료 첨가제</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -17510,29 +17510,29 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -17542,29 +17542,29 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17591,12 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,29 +17606,29 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -17638,29 +17638,29 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
@@ -17719,12 +17719,12 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17734,51 +17734,51 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -17805,22 +17805,22 @@
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -17830,29 +17830,29 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
@@ -17879,44 +17879,44 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -17926,19 +17926,19 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -17965,12 +17965,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -17990,19 +17990,19 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -18029,12 +18029,12 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -18054,19 +18054,19 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -18093,54 +18093,54 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18167,76 +18167,76 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18263,66 +18263,66 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -18342,19 +18342,19 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -18369,34 +18369,34 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18423,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,29 +18470,29 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,29 +18502,29 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -18551,12 +18551,12 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -18583,12 +18583,12 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,29 +18598,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,19 +18662,19 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -18694,29 +18694,29 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,19 +18758,19 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -18790,19 +18790,19 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -18822,29 +18822,29 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,29 +18854,29 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18886,29 +18886,29 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -18918,29 +18918,29 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -18967,12 +18967,12 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18999,12 +18999,12 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -19013,70 +19013,6 @@
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F124" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -2657,7 +2657,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050, 3000, 8040</t>
+          <t xml:space="preserve">3050, 8040</t>
         </is>
       </c>
     </row>
@@ -17463,12 +17463,12 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -17478,29 +17478,29 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">첨가제가 아닌 바이오사료 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">423</t>
+          <t xml:space="preserve">429</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
         </is>
       </c>
     </row>
@@ -17527,12 +17527,12 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
+          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
         </is>
       </c>
     </row>
@@ -17559,12 +17559,12 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -17574,29 +17574,29 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
@@ -17623,12 +17623,12 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
@@ -17655,12 +17655,12 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -17702,39 +17702,39 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
@@ -17751,54 +17751,54 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
@@ -17815,22 +17815,22 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
@@ -17847,12 +17847,12 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17862,29 +17862,29 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -17926,29 +17926,29 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
@@ -17975,12 +17975,12 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,29 +17990,29 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -18022,7 +18022,7 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
@@ -18039,12 +18039,12 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -18054,39 +18054,39 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
@@ -18103,22 +18103,22 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18135,12 +18135,12 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,39 +18150,39 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
@@ -18199,22 +18199,22 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18231,12 +18231,12 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,39 +18246,39 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
@@ -18295,44 +18295,44 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -18359,12 +18359,12 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -18391,12 +18391,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18423,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,29 +18438,29 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -18551,12 +18551,12 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,19 +18566,19 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
@@ -18615,12 +18615,12 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,29 +18662,29 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18775,12 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,29 +18790,29 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18822,19 +18822,19 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -18854,29 +18854,29 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -18935,12 +18935,12 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18950,7 +18950,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18967,12 +18967,12 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -18981,38 +18981,6 @@
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F122" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -2714,7 +2714,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010, 2000, 8040</t>
+          <t xml:space="preserve">2010, 8040</t>
         </is>
       </c>
     </row>
@@ -17527,12 +17527,12 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -17542,29 +17542,29 @@
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 개발분</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">429</t>
+          <t xml:space="preserve">431</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 소재</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17591,12 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
+          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
         </is>
       </c>
     </row>
@@ -17623,12 +17623,12 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품 첨가물</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -17638,7 +17638,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
+          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
         </is>
       </c>
     </row>
@@ -17655,12 +17655,12 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -17670,39 +17670,39 @@
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">432</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">건강기능식품 제품 개발</t>
         </is>
       </c>
     </row>
@@ -17719,54 +17719,54 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강 기능 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">432</t>
+          <t xml:space="preserve">433</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3020</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
         </is>
       </c>
     </row>
@@ -17783,22 +17783,22 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">3040</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물 및 효소</t>
+          <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
+          <t xml:space="preserve">발효식품 제품기술 개발</t>
         </is>
       </c>
     </row>
@@ -17815,12 +17815,12 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효 식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -17830,29 +17830,29 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
+          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
         </is>
       </c>
     </row>
@@ -17879,12 +17879,12 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17894,29 +17894,29 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">435</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
         </is>
       </c>
     </row>
@@ -17943,12 +17943,12 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -17958,29 +17958,29 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">439</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
         </is>
       </c>
     </row>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오식품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -18022,39 +18022,39 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">439</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
+          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">동물용 바이오백신 개발</t>
         </is>
       </c>
     </row>
@@ -18071,22 +18071,22 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18103,12 +18103,12 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -18118,39 +18118,39 @@
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
@@ -18167,22 +18167,22 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18199,12 +18199,12 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18214,39 +18214,39 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
@@ -18263,44 +18263,44 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -18327,12 +18327,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -18359,12 +18359,12 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -18391,12 +18391,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,29 +18406,29 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,19 +18534,19 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
@@ -18583,12 +18583,12 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,29 +18598,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
@@ -18679,12 +18679,12 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,29 +18694,29 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
@@ -18743,12 +18743,12 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,29 +18758,29 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,19 +18790,19 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -18822,29 +18822,29 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -18871,12 +18871,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18935,12 +18935,12 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -18949,38 +18949,6 @@
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3113,7 +3113,7 @@
       </c>
       <c r="K53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120, 8030, 8040</t>
+          <t xml:space="preserve">1120, 8040</t>
         </is>
       </c>
     </row>
@@ -18071,12 +18071,12 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -18086,39 +18086,39 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">441</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">1120</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
         </is>
       </c>
     </row>
@@ -18135,22 +18135,22 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 바이오의약품</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
+          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
         </is>
       </c>
     </row>
@@ -18167,12 +18167,12 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18182,39 +18182,39 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
@@ -18231,44 +18231,44 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -18327,12 +18327,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -18359,12 +18359,12 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,29 +18374,29 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18423,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -18502,19 +18502,19 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
@@ -18551,12 +18551,12 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,29 +18566,29 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,29 +18598,29 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
@@ -18647,12 +18647,12 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,29 +18662,29 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
@@ -18711,12 +18711,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,29 +18726,29 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -18758,19 +18758,19 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -18790,29 +18790,29 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -18839,12 +18839,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -18871,12 +18871,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18903,12 +18903,12 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -18917,38 +18917,6 @@
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3170,7 +3170,7 @@
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120, 8030, 8040</t>
+          <t xml:space="preserve">1120, 8040</t>
         </is>
       </c>
     </row>
@@ -18135,12 +18135,12 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18150,39 +18150,39 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">계약에 따른 비임상 연구개발·효능평가</t>
+          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">451</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">조건부</t>
+          <t xml:space="preserve">핵심</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
+          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
         </is>
       </c>
     </row>
@@ -18199,44 +18199,44 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">핵심</t>
+          <t xml:space="preserve">조건부</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">451</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">2040</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
         </is>
       </c>
     </row>
@@ -18263,12 +18263,12 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2040</t>
+          <t xml:space="preserve">2010</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
+          <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
+          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
         </is>
       </c>
     </row>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 고분자 제품</t>
+          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
+          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
         </is>
       </c>
     </row>
@@ -18327,12 +18327,12 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18342,29 +18342,29 @@
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
+          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
         </is>
       </c>
     </row>
@@ -18391,12 +18391,12 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">4030</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -18406,7 +18406,7 @@
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
+          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18423,12 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4030</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
+          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
+          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -18470,19 +18470,19 @@
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
+          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">461</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -18502,7 +18502,7 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
+          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
         </is>
       </c>
     </row>
@@ -18519,12 +18519,12 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -18534,29 +18534,29 @@
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
+          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">462</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
+          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8040</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -18566,29 +18566,29 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
+          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
+          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 연구개발 서비스</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
+          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
         </is>
       </c>
     </row>
@@ -18615,12 +18615,12 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -18630,29 +18630,29 @@
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
+          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
+          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
         </is>
       </c>
     </row>
@@ -18679,12 +18679,12 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -18694,29 +18694,29 @@
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
+          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000</t>
+          <t xml:space="preserve">4010</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
+          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -18726,19 +18726,19 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
+          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
+          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -18758,29 +18758,29 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
+          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
+          <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">8020</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
+          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
+          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
         </is>
       </c>
     </row>
@@ -18807,12 +18807,12 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8030</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
         </is>
       </c>
     </row>
@@ -18839,12 +18839,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18871,12 +18871,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8050</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -18885,38 +18885,6 @@
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3740,7 +3740,7 @@
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020, 8030, 8050, 8000</t>
+          <t xml:space="preserve">8050, 8000</t>
         </is>
       </c>
     </row>
@@ -18775,12 +18775,12 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8020</t>
+          <t xml:space="preserve">8050</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
+          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유전체·단백질·대사체의 생물학적 분석·진단 서비스에 해당하는 부분</t>
+          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
         </is>
       </c>
     </row>
@@ -18807,12 +18807,12 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8030</t>
+          <t xml:space="preserve">8000</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">임상ㆍ비임상 연구개발 서비스</t>
+          <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -18821,70 +18821,6 @@
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 비임상 시험의 계약 수탁분</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8000</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 바이오서비스업</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
         </is>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -3802,7 +3802,8 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="58" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="110" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3835,6 +3836,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">English definition</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">5차 코드</t>
         </is>
       </c>
@@ -3860,7 +3866,8 @@
           <t xml:space="preserve">Green Bio Production</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
@@ -3887,7 +3894,8 @@
           <t xml:space="preserve">Green Bio Seed Production</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
@@ -3916,6 +3924,11 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that multiply, collect, or raise seeds to produce seeds to which green-bio has been applied. Seeds include grains, mushroom spawn, seedlings, spores, and vegetative propagules used for propagation or cultivation.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">210</t>
         </is>
       </c>
@@ -3941,7 +3954,8 @@
           <t xml:space="preserve">Production of Plants for Green Bio Materials</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
         </is>
@@ -3970,6 +3984,11 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that cultivate and produce cannabis (Cannabis sativa L.) for use as a raw material in manufacturing green-bio materials. Cultivation for fiber or seed collection requires a cannabis cultivator permit. Cultivation for cannabidiol or other materials requires a separate legal basis, such as a regulatory sandbox demonstration exemption. Cultivation unrelated to the manufacture of green-bio materials is excluded. Extraction and processing of cannabis-derived materials are classified under 211.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">221</t>
         </is>
       </c>
@@ -3997,6 +4016,11 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that cultivate and produce plants other than cannabis for use as raw materials in manufacturing green-bio materials, where biotechnology-related techniques have been applied or the plants meet verified green-bio manufacturing specifications. Processing cultivated plants into materials by extraction, drying, milling, or similar methods is classified under 211. Cultivation of ordinary food or ornamental crops is excluded.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">229</t>
         </is>
       </c>
@@ -4022,7 +4046,8 @@
           <t xml:space="preserve">Green Bio Laboratory Animal Production</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="10"/>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">23</t>
         </is>
@@ -4051,6 +4076,11 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that breed and multiply laboratory animals used or reared for animal experiments while maintaining their biological identity and reproductive capacity. This class is limited to production that supplies research, development, or testing in green-bio fields such as veterinary medicines, agricultural inputs, and foods. Production supplied solely to fields outside green-bio, such as the development of medicines for human use, is excluded.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">230</t>
         </is>
       </c>
@@ -4076,7 +4106,8 @@
           <t xml:space="preserve">Other Green Bio Production</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
@@ -4105,6 +4136,11 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to culture, multiply, or rear other agricultural biological resources of actual or potential value to agriculture, such as microorganisms and insects, while maintaining their biological identity and reproductive capacity, where they are not classified in the preceding classes. Processing cultured or multiplied biological resources into non-reproductive materials by killing, drying, milling, extraction, or similar methods is classified in the applicable class of Group 21.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">290</t>
         </is>
       </c>
@@ -4130,7 +4166,8 @@
           <t xml:space="preserve">Green Bio Manufacturing</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="10"/>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
@@ -4157,7 +4194,8 @@
           <t xml:space="preserve">Green Bio Material Manufacturing</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="10"/>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
         </is>
@@ -4186,6 +4224,11 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture green-bio materials, meaning raw materials or intermediate products used to produce green-bio products, by extracting, separating, purifying, fermenting, concentrating, drying, milling, or otherwise processing substances derived from plants or their cell or tissue cultures. Material origin is determined by the output: if the output is a microbial metabolite or microbial biomass, it is classified under 212 even when plant inputs serve as the culture medium or nutrient source. Cultivation of the plants themselves is classified in the applicable class of Group 12.</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">311</t>
         </is>
       </c>
@@ -4213,6 +4256,11 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that culture or ferment microorganisms that are agricultural biological resources of actual or potential value to agriculture, or separate, purify, or process their metabolites or cellular components, to manufacture non-reproductive raw materials or intermediate products used to produce green-bio products. Culturing or multiplying mushroom spawn or microbial strains that retain their biological identity and reproductive capacity is classified under 190.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">312</t>
         </is>
       </c>
@@ -4240,6 +4288,11 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that dry, mill, extract, separate, purify, or otherwise process insects, as defined in Class 413, or insect-derived substances into green-bio materials used as raw materials or intermediate products for producing green-bio products. Rearing and multiplying live insects is classified under 190.</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">313</t>
         </is>
       </c>
@@ -4267,6 +4320,11 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture other green-bio materials, meaning raw materials or intermediate products used to produce green-bio products, that are not classified as materials derived from plants, microorganisms, or insects. Materials with two or more origins are included. Manufacture of food additives is classified under 231.</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">319</t>
         </is>
       </c>
@@ -4292,7 +4350,8 @@
           <t xml:space="preserve">Green Bio Agricultural Input Manufacturing</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
         </is>
@@ -4321,6 +4380,11 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture pesticides used to control crop pests and diseases or regulate crop growth by using living organisms such as microorganisms or insects, or biologically derived substances such as natural substances.</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">321</t>
         </is>
       </c>
@@ -4348,6 +4412,11 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture fertilizers, including soil improvement materials, used to supply plant nutrients or improve soil by using live microorganisms or their metabolites.</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">322</t>
         </is>
       </c>
@@ -4375,6 +4444,11 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture animal feed, including single-ingredient feed, compound feed, and supplementary feed, to supply animal nutrition by using living organisms such as microorganisms or insects, biologically derived substances such as natural substances, or fermentation or enzyme technologies. Veterinary medicines are excluded.</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">323</t>
         </is>
       </c>
@@ -4402,6 +4476,11 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture other green-bio agricultural inputs not classified as biopesticides, biofertilizers, or bio-based animal feed. This includes agricultural films and seedling containers made from biodegradable materials produced using biological resources or microbial fermentation; livestock-facility environmental improvers using microorganisms or natural substances; and crop-growth promoting materials that are neither fertilizers nor pesticides. Seed production is classified under 110, and manufacture of veterinary medicines under 240. Agricultural machinery, facilities, and equipment, and petroleum-derived materials to which green-bio makes no contribution, are excluded.</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">329</t>
         </is>
       </c>
@@ -4427,7 +4506,8 @@
           <t xml:space="preserve">Green Bio Food Manufacturing</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
         </is>
@@ -4456,6 +4536,11 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to manufacture food additives used in the manufacture, processing, preparation, or preservation of food for purposes such as sweetening, coloring, bleaching, or preventing oxidation. All biological origins are covered, including enzymes, sweeteners, and preservatives produced by microbial fermentation. Manufacture of raw materials or intermediate products for food manufacture that are not food additives is classified in the applicable class of Group 21.</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">331</t>
         </is>
       </c>
@@ -4483,6 +4568,11 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture fermented foods by inoculating selected or improved microorganisms or strains, or by directly applying fermentation process control technology. Manufacture of ordinary fermented foods using only spontaneous fermentation is excluded.</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">332</t>
         </is>
       </c>
@@ -4510,6 +4600,11 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to manufacture health functional foods from ingredients or components with functions beneficial to the human body. Ordinary health supplements are excluded.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">333</t>
         </is>
       </c>
@@ -4537,6 +4632,11 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to manufacture special nutritional foods meeting the nutritional needs of specific population groups, such as infants, older adults, or pregnant women, or foods for special medical purposes intended for the dietary or nutritional management of people with diseases or medical conditions.</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">334</t>
         </is>
       </c>
@@ -4564,6 +4664,11 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture foods replacing the texture, flavor, nutrition, or function of conventional livestock or fishery products by using biological resources or materials such as plants, microorganisms, insects, and their cell-culture products, or by using biological processes.</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">335</t>
         </is>
       </c>
@@ -4591,6 +4696,11 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that directly use biological resources, biological materials, or biological processes to manufacture other foods not classified in the preceding classes.</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">339</t>
         </is>
       </c>
@@ -4616,7 +4726,8 @@
           <t xml:space="preserve">Green Bio Veterinary Medicine Manufacturing</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="10"/>
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
         </is>
@@ -4645,6 +4756,11 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to manufacture medicines and pharmaceutical preparations intended solely for animal use.</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">340</t>
         </is>
       </c>
@@ -4670,7 +4786,8 @@
           <t xml:space="preserve">Other Green Bio Product Manufacturing</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E34" s="10"/>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
         </is>
@@ -4699,6 +4816,11 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture cosmetics, including functional and customized cosmetics, and personal care products applied directly to the human body, such as body cleansers and oral care products, using green-bio materials derived from microorganisms, insects, natural substances, or similar sources. Household products not applied directly to the human body are classified under 292. Products made by simply mixing natural ingredients are excluded.</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">391</t>
         </is>
       </c>
@@ -4726,6 +4848,11 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that manufacture household goods using green-bio materials derived from microorganisms, insects, natural substances, or similar sources. This includes household chemical products used to clean, wash, deodorize, disinfect, or repel pests in living spaces or on textiles and objects, and consumer goods such as leather substitutes, fibers, packaging, and cushioning made from green-bio materials. Personal care products applied directly to the human body are classified under 291; manufacture at the material stage, such as fabrics or molded forms, is classified in the applicable class of Group 21. Products made by simply mixing natural ingredients are excluded.</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">392</t>
         </is>
       </c>
@@ -4753,6 +4880,11 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that directly use green-bio to manufacture other green-bio products not classified in the preceding classes.</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">399</t>
         </is>
       </c>
@@ -4778,7 +4910,8 @@
           <t xml:space="preserve">Green Bio Sales and Distribution</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="10"/>
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
@@ -4805,7 +4938,8 @@
           <t xml:space="preserve">Green Bio Biological Resource and Material Sales and Distribution</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="10"/>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
         </is>
@@ -4834,6 +4968,11 @@
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that purchase and sell to businesses or consumers living biological resources, including seeds, planting stock, seedlings, mushroom spawn, microbial strains, cell lines, and industrial insects, or green-bio materials such as extracts, fermentation products, and functional ingredients, or broker their trade for a fee or under contract without taking ownership of the goods. Green-bio materials are raw materials or intermediate products used to produce green-bio products. Direct sales of biological resources or materials produced by the seller are classified in the applicable class of Division 1 or 2. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">410</t>
         </is>
       </c>
@@ -4859,7 +4998,8 @@
           <t xml:space="preserve">Green Bio Agricultural Input Sales</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="10"/>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
         </is>
@@ -4888,6 +5028,11 @@
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a registered pesticide seller that purchases and sells pesticides produced using green-bio to businesses or consumers. Sales businesses dealing only in chemical pesticides are excluded. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">421</t>
         </is>
       </c>
@@ -4915,6 +5060,11 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a fertilizer seller that sells fertilizers produced using green-bio. Sales businesses dealing only in ordinary fertilizers for which the application of biotechnology-related techniques cannot be confirmed are excluded. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">422</t>
         </is>
       </c>
@@ -4942,6 +5092,11 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a feed seller that sells animal feed produced using green-bio. Sales businesses dealing only in ordinary feed for which the application of biotechnology-related techniques cannot be confirmed are excluded. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">423</t>
         </is>
       </c>
@@ -4969,6 +5124,11 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that sell or distribute other green-bio agricultural inputs not covered by the preceding classes. Sales and distribution of seeds are classified under 310, and those of veterinary medicines in the applicable class of Group 34. Sales of agricultural machinery, facilities, and equipment, and businesses dealing only in ordinary agricultural inputs for which the application of biotechnology-related techniques cannot be confirmed, are excluded. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">429</t>
         </is>
       </c>
@@ -4994,7 +5154,8 @@
           <t xml:space="preserve">Green Bio Food Sales</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="10"/>
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">43</t>
         </is>
@@ -5023,6 +5184,11 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a health functional food seller that sells health functional foods produced using green-bio. Sales by dividing or combining products according to an individual's lifestyle or health status are classified under 332; distribution under the seller's own brand of products manufactured under contract is classified under 333. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">431</t>
         </is>
       </c>
@@ -5050,6 +5216,11 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a customized health functional food seller that divides or combines health functional foods produced using green-bio according to an individual's lifestyle, health status, or similar characteristics and sells them. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">432</t>
         </is>
       </c>
@@ -5077,6 +5248,11 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that commission a manufacturer to manufacture or process foods or food additives using green-bio, without manufacturing or processing them directly, and distribute or sell the resulting products under the seller's own brand. Specialized food distribution and sales businesses handling green-bio foods are included. Contract production using raw materials supplied for the seller's own account is classified in the applicable manufacturing class of Division 2. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">433</t>
         </is>
       </c>
@@ -5104,6 +5280,11 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that sell or distribute foods and food materials produced using green-bio that are not covered by the preceding classes. This includes wholesale trade in food materials and additives, and food sales businesses handling green-bio foods. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">439</t>
         </is>
       </c>
@@ -5129,7 +5310,8 @@
           <t xml:space="preserve">Green Bio Veterinary Medicine Sales and Distribution</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="10"/>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
         </is>
@@ -5158,6 +5340,11 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a licensed veterinary medicine wholesaler that purchases veterinary medicines produced using green-bio and sells them to businesses or brokers their trade. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">441</t>
         </is>
       </c>
@@ -5185,6 +5372,11 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities of a veterinary medicine contract-manufacturing seller that commissions the manufacture of green-bio veterinary medicines and distributes or sells them under its own brand. Contract production using raw materials supplied for the seller's own account is classified under 240. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">442</t>
         </is>
       </c>
@@ -5210,7 +5402,8 @@
           <t xml:space="preserve">Other Green Bio Sales and Distribution</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="10"/>
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">49</t>
         </is>
@@ -5239,6 +5432,11 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that purchase and sell to businesses or consumers other green-bio products produced using green-bio that are not covered by the preceding groups. This includes distribution of green-bio cosmetics, personal care and household products, and retail sales of green-bio veterinary medicines by animal pharmacies. Goods are treated as green-bio goods when they were produced or manufactured through activities in Division 1 or 2. This class applies only when the green-bio portion of the goods handled and the related sales can be distinguished from general merchandise. It excludes general retailers and brokerage platforms whose green-bio goods form only an inseparable part of their product range, as well as simple transportation and storage.</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">490</t>
         </is>
       </c>
@@ -5264,7 +5462,8 @@
           <t xml:space="preserve">Green Bio Research and Development</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E56" s="10"/>
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
@@ -5291,7 +5490,8 @@
           <t xml:space="preserve">Green Bio Biological Resource Research and Development</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E57" s="10"/>
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
@@ -5320,6 +5520,11 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to breed new seeds or varieties, or research and develop the traits, functions, propagation processes, safety, or uses of grains, mushroom spawn, seedlings, spores, and vegetative propagules used for propagation or cultivation. This includes research and development on the varieties, traits, and safety of genetically modified plants, as well as radiation breeding, polyploid breeding, genomic breeding, and digital breeding.</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">111</t>
         </is>
       </c>
@@ -5347,6 +5552,11 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to discover or improve living microorganisms, such as strains and starter cultures used in cultivation, animal rearing, or fermentation for food or agricultural input production, or to research and develop their traits, functions, propagation processes, or uses. Research and development of mushroom spawn used as seed is classified under 411. Research and development that uses microorganisms to create agricultural inputs, foods, medicines, or other outputs is classified in the group corresponding to the output, from Groups 42 through 46.</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">112</t>
         </is>
       </c>
@@ -5374,6 +5584,11 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to discover or improve living insects used in rearing or propagation, or to research and develop their traits, functions, rearing processes, or uses. This includes the development of superior insect breeding stock. Here, insects include stag beetles, rhinoceros beetles, fireflies, black soldier flies, flower chafers, and bumblebees; all animals classified in class Insecta of phylum Arthropoda under the International Code of Zoological Nomenclature; and arachnids and centipedes. Research and development directed at specific outputs such as feed or food is classified in the group corresponding to the output.</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">113</t>
         </is>
       </c>
@@ -5401,6 +5616,11 @@
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities not covered by the preceding classes that use green-bio to research and develop other living agricultural biological resources of actual or potential value to agriculture, including their traits, functions, propagation processes, and uses.</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">119</t>
         </is>
       </c>
@@ -5426,7 +5646,8 @@
           <t xml:space="preserve">Green Bio Agricultural Input Research and Development</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E62" s="10"/>
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
@@ -5455,6 +5676,11 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use living organisms such as microorganisms or insects, or biologically derived substances such as natural substances, to research and develop pesticides for crop pest and disease control or growth regulation, including their materials, formulations, production processes, efficacy, and safety.</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">121</t>
         </is>
       </c>
@@ -5482,6 +5708,11 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use live microorganisms or their metabolites to research and develop fertilizers for plant nutrition or soil improvement, including their materials, formulations, production processes, and efficacy. This includes research and development of microbial preparations for soil improvement, such as soil improvement materials and by-product fertilizers.</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">122</t>
         </is>
       </c>
@@ -5509,6 +5740,11 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use living organisms such as microorganisms or insects, biologically derived substances such as natural substances, or fermentation or enzyme technologies to research and develop animal feed, including single-ingredient feed, compound feed, and supplementary feed, and its materials, formulations, production processes, or efficacy. Research and development intended for veterinary medicines is classified in Group 44.</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">123</t>
         </is>
       </c>
@@ -5536,6 +5772,11 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that research and develop other green-bio agricultural inputs not classified as biopesticides, biofertilizers, or bio-based animal feed, including their materials, production processes, or efficacy. This includes agricultural films and seedling containers made from biodegradable materials produced using biological resources or microbial fermentation; livestock-facility environmental improvers using microorganisms or natural substances; and crop-growth promoting materials that are neither fertilizers nor pesticides. Seeds are classified under 411, and veterinary medicines in Group 44. Research and development of agricultural machinery, facilities, and equipment, and petroleum-derived materials to which green-bio makes no contribution, are excluded.</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">129</t>
         </is>
       </c>
@@ -5561,7 +5802,8 @@
           <t xml:space="preserve">Research and Development of Green Bio Food Ingredients and Products</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E67" s="10"/>
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
@@ -5590,6 +5832,11 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that develop natural substances and other materials derived from living organisms such as microorganisms, insects, and plants as raw materials or intermediate products for food manufacture, and research and develop their composition, functions, extraction, separation, purification, standardization, mass production, or uses. Both functional and other food materials are included. Research and development of materials intended for alternative foods is classified under 434; fermentation processes or microbial utilization technologies themselves under 433; and materials intended for cosmetics or household products in Group 45.</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">131</t>
         </is>
       </c>
@@ -5617,6 +5864,11 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop the composition, formulation, functionality, safety, or product technology of health functional foods made from ingredients or components with functions beneficial to the human body. Research and development at the raw-material or intermediate-product stage is classified under 431.</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">132</t>
         </is>
       </c>
@@ -5644,6 +5896,11 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that research and develop technologies for using microorganisms in food manufacture, processing, or fermentation, as well as fermentation processes, enzymes, safety, or product technologies for fermented foods. Discovery or improvement of microbial strains themselves is classified under 412.</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">133</t>
         </is>
       </c>
@@ -5671,6 +5928,11 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop foods replacing the texture, flavor, nutrition, or function of conventional livestock or fishery products, including their materials, formulations, structuring processes, safety, and product technologies. This includes research and development of plant- or seaweed-based meat alternatives, cultured meat from animal cells, insect alternative proteins, and microbial-fermentation alternative proteins, regardless of the source material or method.</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">134</t>
         </is>
       </c>
@@ -5698,6 +5960,11 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop special nutritional foods meeting the nutritional needs of specific population groups, such as infants, older adults, or pregnant women, or foods for special medical purposes intended for the dietary or nutritional management of people with diseases or medical conditions, including their materials, formulations, and manufacturing processes.</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">135</t>
         </is>
       </c>
@@ -5725,6 +5992,11 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that research and develop other green-bio foods and food materials not covered by the preceding classes.</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">139</t>
         </is>
       </c>
@@ -5750,7 +6022,8 @@
           <t xml:space="preserve">Green Bio Veterinary Medicine Research and Development</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="10"/>
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
@@ -5779,6 +6052,11 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop antigens, immunogens, vaccine strains, vectors, adjuvants, formulations, production processes, efficacy, safety, or administration technologies for medicines intended solely for animal use to prevent infectious animal diseases.</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">141</t>
         </is>
       </c>
@@ -5806,6 +6084,11 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that research and develop candidate substances, active ingredients, diagnostic agents, therapeutics, formulations, production processes, efficacy, safety, or uses of other green-bio veterinary medicines not classified as veterinary vaccine research and development.</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">149</t>
         </is>
       </c>
@@ -5831,7 +6114,8 @@
           <t xml:space="preserve">Research and Development of Green Bio Cosmetics and Household Products</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="10"/>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
@@ -5860,6 +6144,11 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop cosmetics, including functional and customized cosmetics, and personal care products applied directly to the human body, such as body cleansers and oral care products, as well as materials used to manufacture them, formulations, efficacy, or safety.</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">151</t>
         </is>
       </c>
@@ -5887,6 +6176,11 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use green-bio to research and develop household goods and the materials, formulations, or efficacy involved in their manufacture. This includes household chemical products for cleaning, washing, deodorizing, antimicrobial treatment, or pest control in living spaces or on textiles and objects, and consumer goods such as leather substitutes, fibers, packaging, and cushioning made from green-bio materials. Personal care products applied directly to the human body are classified under 451; research and development of the materials themselves is classified under 431 or 490.</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">152</t>
         </is>
       </c>
@@ -5912,7 +6206,8 @@
           <t xml:space="preserve">Research and Development of Green Bio Environmental and Digital Services</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="E80" s="10"/>
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
@@ -5941,6 +6236,11 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use living biological resources such as insects or microorganisms to research and develop technologies, processes, or preparations for treating organic waste resources; controlling pests and diseases; or managing and improving agricultural environments such as livestock facilities, farmland, and agricultural water. Research and development intended for pesticide preparations is classified under 421; fertilizer or soil-improvement preparations under 422; and discovery or improvement of the biological resources themselves in the applicable class of Group 41. The provision of environmental services itself is classified in the applicable class of Group 53.</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">161</t>
         </is>
       </c>
@@ -5968,6 +6268,11 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that research and develop technologies for analyzing agricultural bio-resource data, such as genomic and phenotypic data, and digital technologies including digital breeding platforms, software for the green-bio industry, and artificial intelligence models. Research and development that uses molecular markers or genomic analysis to breed varieties themselves is classified under 411; provision of data services itself is classified in the applicable class of Group 52.</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">162</t>
         </is>
       </c>
@@ -5993,7 +6298,8 @@
           <t xml:space="preserve">Other Green Bio Research and Development</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E83" s="10"/>
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
@@ -6022,6 +6328,11 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Other green-bio research and development activities not covered by the preceding groups. This includes research and development of multipurpose materials or platform technologies for which no particular application has been specified. Research and development of data or digital technologies is classified under 462.</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">190</t>
         </is>
       </c>
@@ -6047,7 +6358,8 @@
           <t xml:space="preserve">Green Bio Information, Environmental and Other Services</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E85" s="10"/>
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
@@ -6074,7 +6386,8 @@
           <t xml:space="preserve">Green Bio Information and Data Services</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E86" s="10"/>
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">52</t>
         </is>
@@ -6103,6 +6416,11 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that provide genomic, marker, or phenotypic analysis and bioinformatics consulting services to support digital breeding by analyzing genomic information and other data on agricultural bio-resources. Services provided by digital breeding consulting and analysis specialist institutions designated by the Ministry of Agriculture, Food and Rural Affairs are included. Research and development that breeds varieties themselves is classified under 411; research and development of analysis technologies or platforms themselves is classified under 462.</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">521</t>
         </is>
       </c>
@@ -6130,6 +6448,11 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that collect, analyze, process, and provide other data relating to green-bio that are not covered by the preceding class. Operation of bioinformatics databases and platforms is included. Research and development in which data analysis leads to the development of new varieties, materials, products, or technologies is classified in the applicable class of Division 4.</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">529</t>
         </is>
       </c>
@@ -6155,7 +6478,8 @@
           <t xml:space="preserve">Green Bio Environmental Services</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
+      <c r="E89" s="10"/>
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">53</t>
         </is>
@@ -6184,6 +6508,11 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that apply biotechnology-related techniques to living biological resources such as insects or microorganisms to break down and treat agricultural organic waste resources, including livestock manure and food waste. This class applies when treatment fees are the principal source of revenue. Manufacture of larval feed produced during treatment is classified under 223, and manufacture of fertilizer from insect frass under 222.</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">531</t>
         </is>
       </c>
@@ -6211,6 +6540,11 @@
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that use living biological resources such as natural enemy insects or microorganisms as the principal means of controlling crop pests and diseases or managing and improving the environment of livestock facilities, farmland, or agricultural water by designing and implementing programs based on biotechnology-related techniques and the organisms' biological characteristics. This includes biological pest control using natural enemies or microorganisms. It excludes contractors that merely apply purchased biopesticides or environmental improvers without biological program design, pest control using only chemical pesticides, and remediation of general industrial wastewater or contaminated soil unrelated to agriculture.</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">532</t>
         </is>
       </c>
@@ -6236,7 +6570,8 @@
           <t xml:space="preserve">Other Green Bio Services</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E92" s="10"/>
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">59</t>
         </is>
@@ -6265,13 +6600,18 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Industrial activities that provide other green-bio-related services not covered by the preceding groups. This includes services that use standardized methods to test, inspect, or analyze the quality, composition, functionality, safety, or efficacy of green-bio goods such as seeds, microorganisms, insects, natural substances, foods, and veterinary medicines, including seed testing, microbial identification, genetic or compositional analysis, and contracted nonclinical testing of veterinary medicines; services that inspect, review, and certify whether green-bio goods or their production and manufacturing processes comply with laws, specifications, or standards; and storage or transport services specialized in preserving the identity of biological resources such as seeds and microbial strains. Contract research aimed at developing new varieties, materials, products, or technologies is classified in the applicable class of Division 4; genomic or bioinformatics analysis services supporting digital breeding are classified under 521. Simple transportation and storage are excluded. Education or training about green-bio technologies is also excluded because it conveys knowledge rather than applying biotechnology and belongs to the workforce development support system rather than an industrial activity.</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">590</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -305,7 +305,7 @@
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Seed Production</t>
+          <t xml:space="preserve">Green-Bio Seed Production</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr">
@@ -362,7 +362,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannabis Cultivation for Green Bio Materials</t>
+          <t xml:space="preserve">Cannabis Cultivation for Green-Bio Materials</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -419,7 +419,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production of Other Plants for Green Bio Materials</t>
+          <t xml:space="preserve">Production of Other Plants for Green-Bio Materials</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Laboratory Animal Production</t>
+          <t xml:space="preserve">Green-Bio Laboratory Animal Production</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Production</t>
+          <t xml:space="preserve">Other Green-Bio Production</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Plants</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Plants</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Microorganisms</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Microorganisms</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Insects</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Insects</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Material Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Material Manufacturing</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Manufacturing</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Additive Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Food Additive Manufacturing</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Fermented Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Fermented Food Manufacturing</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Manufacturing</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Alternative Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Alternative Food Manufacturing</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Food Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Food Manufacturing</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Manufacturing</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Cosmetics and Personal Care Products</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Cosmetics and Personal Care Products</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Household Product Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Household Product Manufacturing</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Product Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Product Manufacturing</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Biological Resource and Material Sales and Distribution</t>
+          <t xml:space="preserve">Green-Bio Biological Resource and Material Sales and Distribution</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Sales</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Sales</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Sales</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Sales</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customized Green Bio Health Functional Food Sales</t>
+          <t xml:space="preserve">Customized Green-Bio Health Functional Food Sales</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specialized Distribution and Sales of Green Bio Foods</t>
+          <t xml:space="preserve">Specialized Distribution and Sales of Green-Bio Foods</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Food Sales</t>
+          <t xml:space="preserve">Other Green-Bio Food Sales</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Wholesale</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Wholesale</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales of Contract-Manufactured Green Bio Veterinary Medicines</t>
+          <t xml:space="preserve">Sales of Contract-Manufactured Green-Bio Veterinary Medicines</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Sales and Distribution</t>
+          <t xml:space="preserve">Other Green-Bio Sales and Distribution</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Seed Research and Development</t>
+          <t xml:space="preserve">Green-Bio Seed Research and Development</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Microorganism Research and Development</t>
+          <t xml:space="preserve">Green-Bio Microorganism Research and Development</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Insect Research and Development</t>
+          <t xml:space="preserve">Green-Bio Insect Research and Development</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Other Green Bio Biological Resources</t>
+          <t xml:space="preserve">Research and Development of Other Green-Bio Biological Resources</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Research and Development</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Ingredient Research and Development</t>
+          <t xml:space="preserve">Green-Bio Food Ingredient Research and Development</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Research and Development</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Research and Development</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Fermentation and Microbial Technologies for Food</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Fermentation and Microbial Technologies for Food</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Alternative Food Research and Development</t>
+          <t xml:space="preserve">Green-Bio Alternative Food Research and Development</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Research and Development of Green Bio Food Ingredients and Products</t>
+          <t xml:space="preserve">Other Research and Development of Green-Bio Food Ingredients and Products</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Veterinary Medicine Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Veterinary Medicine Research and Development</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Cosmetics and Personal Care Products</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Cosmetics and Personal Care Products</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Household Product Research and Development</t>
+          <t xml:space="preserve">Green-Bio Household Product Research and Development</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Environmental Service Research and Development</t>
+          <t xml:space="preserve">Green-Bio Environmental Service Research and Development</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Digital Service Research and Development</t>
+          <t xml:space="preserve">Green-Bio Digital Service Research and Development</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Research and Development</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="H60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Digital Breeding Services</t>
+          <t xml:space="preserve">Green-Bio Digital Breeding Services</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Information and Data Services</t>
+          <t xml:space="preserve">Other Green-Bio Information and Data Services</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Organic Waste Resource Treatment</t>
+          <t xml:space="preserve">Green-Bio Organic Waste Resource Treatment</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Pest Control and Agricultural Environment Management</t>
+          <t xml:space="preserve">Green-Bio Pest Control and Agricultural Environment Management</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Services</t>
+          <t xml:space="preserve">Other Green-Bio Services</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Industry Special Classification · Round 6</t>
+          <t xml:space="preserve">Green-Bio Industry Special Classification · Round 6</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Production</t>
+          <t xml:space="preserve">Green-Bio Production</t>
         </is>
       </c>
       <c r="E4" s="10"/>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Seed Production</t>
+          <t xml:space="preserve">Green-Bio Seed Production</t>
         </is>
       </c>
       <c r="E5" s="10"/>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Seed Production</t>
+          <t xml:space="preserve">Green-Bio Seed Production</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production of Plants for Green Bio Materials</t>
+          <t xml:space="preserve">Production of Plants for Green-Bio Materials</t>
         </is>
       </c>
       <c r="E7" s="10"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cannabis Cultivation for Green Bio Materials</t>
+          <t xml:space="preserve">Cannabis Cultivation for Green-Bio Materials</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production of Other Plants for Green Bio Materials</t>
+          <t xml:space="preserve">Production of Other Plants for Green-Bio Materials</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Laboratory Animal Production</t>
+          <t xml:space="preserve">Green-Bio Laboratory Animal Production</t>
         </is>
       </c>
       <c r="E10" s="10"/>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Laboratory Animal Production</t>
+          <t xml:space="preserve">Green-Bio Laboratory Animal Production</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Production</t>
+          <t xml:space="preserve">Other Green-Bio Production</t>
         </is>
       </c>
       <c r="E12" s="10"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Production</t>
+          <t xml:space="preserve">Other Green-Bio Production</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Manufacturing</t>
         </is>
       </c>
       <c r="E14" s="10"/>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Material Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Material Manufacturing</t>
         </is>
       </c>
       <c r="E15" s="10"/>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Plants</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Plants</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Microorganisms</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Microorganisms</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Materials Derived from Insects</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Insects</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Material Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Material Manufacturing</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Agricultural Input Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Agricultural Input Manufacturing</t>
         </is>
       </c>
       <c r="E20" s="10"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Manufacturing</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Food Manufacturing</t>
         </is>
       </c>
       <c r="E25" s="10"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Additive Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Food Additive Manufacturing</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Fermented Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Fermented Food Manufacturing</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Manufacturing</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Alternative Food Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Alternative Food Manufacturing</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Food Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Food Manufacturing</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Manufacturing</t>
         </is>
       </c>
       <c r="E32" s="10"/>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Manufacturing</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Product Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Product Manufacturing</t>
         </is>
       </c>
       <c r="E34" s="10"/>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green Bio Cosmetics and Personal Care Products</t>
+          <t xml:space="preserve">Manufacturing of Green-Bio Cosmetics and Personal Care Products</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Household Product Manufacturing</t>
+          <t xml:space="preserve">Green-Bio Household Product Manufacturing</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Product Manufacturing</t>
+          <t xml:space="preserve">Other Green-Bio Product Manufacturing</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Sales and Distribution</t>
+          <t xml:space="preserve">Green-Bio Sales and Distribution</t>
         </is>
       </c>
       <c r="E38" s="10"/>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Biological Resource and Material Sales and Distribution</t>
+          <t xml:space="preserve">Green-Bio Biological Resource and Material Sales and Distribution</t>
         </is>
       </c>
       <c r="E39" s="10"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Biological Resource and Material Sales and Distribution</t>
+          <t xml:space="preserve">Green-Bio Biological Resource and Material Sales and Distribution</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Agricultural Input Sales</t>
+          <t xml:space="preserve">Green-Bio Agricultural Input Sales</t>
         </is>
       </c>
       <c r="E41" s="10"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Sales</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Sales</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Sales</t>
+          <t xml:space="preserve">Green-Bio Food Sales</t>
         </is>
       </c>
       <c r="E46" s="10"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Sales</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Sales</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Customized Green Bio Health Functional Food Sales</t>
+          <t xml:space="preserve">Customized Green-Bio Health Functional Food Sales</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Specialized Distribution and Sales of Green Bio Foods</t>
+          <t xml:space="preserve">Specialized Distribution and Sales of Green-Bio Foods</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Food Sales</t>
+          <t xml:space="preserve">Other Green-Bio Food Sales</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Sales and Distribution</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Sales and Distribution</t>
         </is>
       </c>
       <c r="E51" s="10"/>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Wholesale</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Wholesale</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sales of Contract-Manufactured Green Bio Veterinary Medicines</t>
+          <t xml:space="preserve">Sales of Contract-Manufactured Green-Bio Veterinary Medicines</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Sales and Distribution</t>
+          <t xml:space="preserve">Other Green-Bio Sales and Distribution</t>
         </is>
       </c>
       <c r="E54" s="10"/>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Sales and Distribution</t>
+          <t xml:space="preserve">Other Green-Bio Sales and Distribution</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Research and Development</t>
+          <t xml:space="preserve">Green-Bio Research and Development</t>
         </is>
       </c>
       <c r="E56" s="10"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Biological Resource Research and Development</t>
+          <t xml:space="preserve">Green-Bio Biological Resource Research and Development</t>
         </is>
       </c>
       <c r="E57" s="10"/>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Seed Research and Development</t>
+          <t xml:space="preserve">Green-Bio Seed Research and Development</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Microorganism Research and Development</t>
+          <t xml:space="preserve">Green-Bio Microorganism Research and Development</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Insect Research and Development</t>
+          <t xml:space="preserve">Green-Bio Insect Research and Development</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Other Green Bio Biological Resources</t>
+          <t xml:space="preserve">Research and Development of Other Green-Bio Biological Resources</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Agricultural Input Research and Development</t>
+          <t xml:space="preserve">Green-Bio Agricultural Input Research and Development</t>
         </is>
       </c>
       <c r="E62" s="10"/>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Agricultural Input Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Agricultural Input Research and Development</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Food Ingredients and Products</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Food Ingredients and Products</t>
         </is>
       </c>
       <c r="E67" s="10"/>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Food Ingredient Research and Development</t>
+          <t xml:space="preserve">Green-Bio Food Ingredient Research and Development</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Health Functional Food Research and Development</t>
+          <t xml:space="preserve">Green-Bio Health Functional Food Research and Development</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Fermentation and Microbial Technologies for Food</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Fermentation and Microbial Technologies for Food</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Alternative Food Research and Development</t>
+          <t xml:space="preserve">Green-Bio Alternative Food Research and Development</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Research and Development of Green Bio Food Ingredients and Products</t>
+          <t xml:space="preserve">Other Research and Development of Green-Bio Food Ingredients and Products</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Veterinary Medicine Research and Development</t>
+          <t xml:space="preserve">Green-Bio Veterinary Medicine Research and Development</t>
         </is>
       </c>
       <c r="E74" s="10"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Veterinary Medicine Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Veterinary Medicine Research and Development</t>
         </is>
       </c>
       <c r="E76" s="10" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Cosmetics and Household Products</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Cosmetics and Household Products</t>
         </is>
       </c>
       <c r="E77" s="10"/>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Cosmetics and Personal Care Products</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Cosmetics and Personal Care Products</t>
         </is>
       </c>
       <c r="E78" s="10" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Household Product Research and Development</t>
+          <t xml:space="preserve">Green-Bio Household Product Research and Development</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research and Development of Green Bio Environmental and Digital Services</t>
+          <t xml:space="preserve">Research and Development of Green-Bio Environmental and Digital Services</t>
         </is>
       </c>
       <c r="E80" s="10"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Environmental Service Research and Development</t>
+          <t xml:space="preserve">Green-Bio Environmental Service Research and Development</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Digital Service Research and Development</t>
+          <t xml:space="preserve">Green-Bio Digital Service Research and Development</t>
         </is>
       </c>
       <c r="E82" s="10" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Research and Development</t>
         </is>
       </c>
       <c r="E83" s="10"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Research and Development</t>
+          <t xml:space="preserve">Other Green-Bio Research and Development</t>
         </is>
       </c>
       <c r="E84" s="10" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Information, Environmental and Other Services</t>
+          <t xml:space="preserve">Green-Bio Information, Environmental and Other Services</t>
         </is>
       </c>
       <c r="E85" s="10"/>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Information and Data Services</t>
+          <t xml:space="preserve">Green-Bio Information and Data Services</t>
         </is>
       </c>
       <c r="E86" s="10"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Digital Breeding Services</t>
+          <t xml:space="preserve">Green-Bio Digital Breeding Services</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Information and Data Services</t>
+          <t xml:space="preserve">Other Green-Bio Information and Data Services</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Environmental Services</t>
+          <t xml:space="preserve">Green-Bio Environmental Services</t>
         </is>
       </c>
       <c r="E89" s="10"/>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Organic Waste Resource Treatment</t>
+          <t xml:space="preserve">Green-Bio Organic Waste Resource Treatment</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green Bio Pest Control and Agricultural Environment Management</t>
+          <t xml:space="preserve">Green-Bio Pest Control and Agricultural Environment Management</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Services</t>
+          <t xml:space="preserve">Other Green-Bio Services</t>
         </is>
       </c>
       <c r="E92" s="10"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green Bio Services</t>
+          <t xml:space="preserve">Other Green-Bio Services</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -6625,8 +6625,6 @@
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6657,16 +6655,6 @@
           <t xml:space="preserve">연계 명칭</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -6689,12 +6677,6 @@
           <t xml:space="preserve">종자 및 묘목 생산업</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F4" s="10"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -6717,12 +6699,6 @@
           <t xml:space="preserve">임업용 종묘 생산업</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F5" s="10"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -6745,12 +6721,6 @@
           <t xml:space="preserve">기타 작물 재배업</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F6" s="10"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -6773,12 +6743,6 @@
           <t xml:space="preserve">곡물 및 기타 식량작물 재배업</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F7" s="10"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -6801,12 +6765,6 @@
           <t xml:space="preserve">채소작물 재배업</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F8" s="10"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -6829,12 +6787,6 @@
           <t xml:space="preserve">화훼작물 재배업</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F9" s="10"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -6857,12 +6809,6 @@
           <t xml:space="preserve">과실작물 재배업</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F10" s="10"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6885,12 +6831,6 @@
           <t xml:space="preserve">음료용 및 향신용 작물 재배업</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F11" s="10"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6913,12 +6853,6 @@
           <t xml:space="preserve">기타 작물 재배업</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F12" s="10"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -6941,12 +6875,6 @@
           <t xml:space="preserve">채소, 화훼 및 과실작물 시설 재배업</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F13" s="10"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -6969,12 +6897,6 @@
           <t xml:space="preserve">기타 시설작물 재배업</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F14" s="10"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -6997,12 +6919,6 @@
           <t xml:space="preserve">그 외 기타 축산업</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F15" s="10"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -7025,12 +6941,6 @@
           <t xml:space="preserve">그 외 기타 축산업</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F16" s="10"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -7053,12 +6963,6 @@
           <t xml:space="preserve">기초 의약 물질 제조업</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F17" s="10"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -7081,12 +6985,6 @@
           <t xml:space="preserve">해수면 양식 어업</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F18" s="10"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -7109,12 +7007,6 @@
           <t xml:space="preserve">내수면 양식 어업</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F19" s="10"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -7137,12 +7029,6 @@
           <t xml:space="preserve">수산물 부화 및 수산 종자 생산업</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F20" s="10"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -7165,12 +7051,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F21" s="10"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -7193,12 +7073,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F22" s="10"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -7221,12 +7095,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F23" s="10"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -7249,12 +7117,6 @@
           <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F24" s="10"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -7277,12 +7139,6 @@
           <t xml:space="preserve">기초 의약 물질 제조업</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F25" s="10"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -7305,12 +7161,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F26" s="10"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7333,12 +7183,6 @@
           <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F27" s="10"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -7361,12 +7205,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F28" s="10"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -7389,12 +7227,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F29" s="10"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7417,12 +7249,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F30" s="10"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -7445,12 +7271,6 @@
           <t xml:space="preserve">기초 의약 물질 제조업</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F31" s="10"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7473,12 +7293,6 @@
           <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F32" s="10"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7501,12 +7315,6 @@
           <t xml:space="preserve">한의약품 제조업</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F33" s="10"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7529,12 +7337,6 @@
           <t xml:space="preserve">생물 살균·살충제 및 식물보호제 제조업</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F34" s="10"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7557,12 +7359,6 @@
           <t xml:space="preserve">유기질 비료 및 상토 제조업</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F35" s="10"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7585,12 +7381,6 @@
           <t xml:space="preserve">배합 사료 제조업</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F36" s="10"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7613,12 +7403,6 @@
           <t xml:space="preserve">단미사료 및 기타 사료 제조업</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F37" s="10"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7641,12 +7425,6 @@
           <t xml:space="preserve">반려동물용 사료 제조업</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F38" s="10"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7669,12 +7447,6 @@
           <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F39" s="10"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7697,12 +7469,6 @@
           <t xml:space="preserve">유기질 비료 및 상토 제조업</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F40" s="10"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7725,12 +7491,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F41" s="10"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -7753,12 +7513,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F42" s="10"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -7781,12 +7535,6 @@
           <t xml:space="preserve">식초, 발효 및 화학 조미료 제조업</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F43" s="10"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -7809,12 +7557,6 @@
           <t xml:space="preserve">천연 및 혼합 조제 조미료 제조업</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F44" s="10"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -7837,12 +7579,6 @@
           <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F45" s="10"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -7865,12 +7601,6 @@
           <t xml:space="preserve">김치류 제조업</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F46" s="10"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -7893,12 +7623,6 @@
           <t xml:space="preserve">과실 및 그 외 채소 절임식품 제조업</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F47" s="10"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -7921,12 +7645,6 @@
           <t xml:space="preserve">기타 과실·채소 가공 및 저장 처리업</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F48" s="10"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -7949,12 +7667,6 @@
           <t xml:space="preserve">액상 시유 및 기타 낙농제품 제조업</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F49" s="10"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -7977,12 +7689,6 @@
           <t xml:space="preserve">아이스크림 및 기타 식용 빙과류 제조업</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F50" s="10"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8005,12 +7711,6 @@
           <t xml:space="preserve">식초, 발효 및 화학 조미료 제조업</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F51" s="10"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8033,12 +7733,6 @@
           <t xml:space="preserve">장류 제조업</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F52" s="10"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8061,12 +7755,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F53" s="10"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8089,12 +7777,6 @@
           <t xml:space="preserve">탁주 및 약주 제조업</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F54" s="10"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8117,12 +7799,6 @@
           <t xml:space="preserve">맥아 및 맥주 제조업</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F55" s="10"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -8145,12 +7821,6 @@
           <t xml:space="preserve">기타 발효주 제조업</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F56" s="10"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -8173,12 +7843,6 @@
           <t xml:space="preserve">주정 제조업</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F57" s="10"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -8201,12 +7865,6 @@
           <t xml:space="preserve">건강 기능식품 제조업</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F58" s="10"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -8229,12 +7887,6 @@
           <t xml:space="preserve">인삼식품 제조업</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F59" s="10"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -8257,12 +7909,6 @@
           <t xml:space="preserve">건강 보조용 액화식품 제조업</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F60" s="10"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -8285,12 +7931,6 @@
           <t xml:space="preserve">액상 시유 및 기타 낙농제품 제조업</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F61" s="10"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -8313,12 +7953,6 @@
           <t xml:space="preserve">수프 및 균질화식품 제조업</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F62" s="10"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -8341,12 +7975,6 @@
           <t xml:space="preserve">도시락류 제조업</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F63" s="10"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -8369,12 +7997,6 @@
           <t xml:space="preserve">기타 식사용 가공처리 조리식품 제조업</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F64" s="10"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -8397,12 +8019,6 @@
           <t xml:space="preserve">차류 가공업</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F65" s="10"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -8425,12 +8041,6 @@
           <t xml:space="preserve">그 외 기타 식료품 제조업</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F66" s="10"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -8453,12 +8063,6 @@
           <t xml:space="preserve">곡물 혼합 분말 및 반죽 제조업</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F67" s="10"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -8481,12 +8085,6 @@
           <t xml:space="preserve">기타 곡물 가공품 제조업</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F68" s="10"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -8509,12 +8107,6 @@
           <t xml:space="preserve">전분제품 및 당류 제조업</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F69" s="10"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -8537,12 +8129,6 @@
           <t xml:space="preserve">두부 및 유사 식품 제조업</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F70" s="10"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -8565,12 +8151,6 @@
           <t xml:space="preserve">그 외 기타 식료품 제조업</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F71" s="10"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -8593,12 +8173,6 @@
           <t xml:space="preserve">기타 과실·채소 가공 및 저장 처리업</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F72" s="10"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -8621,12 +8195,6 @@
           <t xml:space="preserve">기타 식사용 가공처리 조리식품 제조업</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F73" s="10"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -8649,12 +8217,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F74" s="10"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -8677,12 +8239,6 @@
           <t xml:space="preserve">그 외 기타 식료품 제조업</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F75" s="10"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -8705,12 +8261,6 @@
           <t xml:space="preserve">동물용 의약품 제조업</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F76" s="10"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -8733,12 +8283,6 @@
           <t xml:space="preserve">기초 의약 물질 제조업</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F77" s="10"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -8761,12 +8305,6 @@
           <t xml:space="preserve">생물 의약품 제조업</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F78" s="10"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -8789,12 +8327,6 @@
           <t xml:space="preserve">화장품 제조업</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F79" s="10"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -8817,12 +8349,6 @@
           <t xml:space="preserve">표면 광택제 및 실내 가향제 제조업</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F80" s="10"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -8845,12 +8371,6 @@
           <t xml:space="preserve">치약, 비누 및 기타 세제 제조업</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F81" s="10"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -8873,12 +8393,6 @@
           <t xml:space="preserve">표면 광택제 및 실내 가향제 제조업</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F82" s="10"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -8901,12 +8415,6 @@
           <t xml:space="preserve">기타 가죽제품 제조업</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F83" s="10"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -8929,12 +8437,6 @@
           <t xml:space="preserve">모피 및 가죽 제조업</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F84" s="10"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -8957,12 +8459,6 @@
           <t xml:space="preserve">혼성 및 재생 플라스틱 소재 물질 제조업</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F85" s="10"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -8985,12 +8481,6 @@
           <t xml:space="preserve">종자 및 묘목 도매업</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F86" s="10"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -9013,12 +8503,6 @@
           <t xml:space="preserve">음·식료품 및 담배 중개업</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F87" s="10"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -9041,12 +8525,6 @@
           <t xml:space="preserve">비료 및 농약 도매업</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F88" s="10"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -9069,12 +8547,6 @@
           <t xml:space="preserve">비료 및 농약 도매업</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F89" s="10"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -9097,12 +8569,6 @@
           <t xml:space="preserve">사료 도매업</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F90" s="10"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -9125,12 +8591,6 @@
           <t xml:space="preserve">비료 및 농약 도매업</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F91" s="10"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -9153,12 +8613,6 @@
           <t xml:space="preserve">사료 도매업</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F92" s="10"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -9181,12 +8635,6 @@
           <t xml:space="preserve">건강 보조식품 소매업</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F93" s="10"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -9209,12 +8657,6 @@
           <t xml:space="preserve">화장품 및 화장용품 도매업</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F94" s="10"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -9237,12 +8679,6 @@
           <t xml:space="preserve">건강 보조식품 소매업</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F95" s="10"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -9265,12 +8701,6 @@
           <t xml:space="preserve">화장품 및 화장용품 도매업</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F96" s="10"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -9293,12 +8723,6 @@
           <t xml:space="preserve">기타 신선 식품 및 단순 가공 식품 도매업</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F97" s="10"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -9321,12 +8745,6 @@
           <t xml:space="preserve">과실류 도매업</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F98" s="10"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -9349,12 +8767,6 @@
           <t xml:space="preserve">기타 신선 식품 및 단순 가공 식품 도매업</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F99" s="10"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -9377,12 +8789,6 @@
           <t xml:space="preserve">곡물, 곡분 및 가축 사료 소매업</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F100" s="10"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -9405,12 +8811,6 @@
           <t xml:space="preserve">기타 신선식품 및 단순 가공식품 소매업</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F101" s="10"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -9433,12 +8833,6 @@
           <t xml:space="preserve">의약품 도매업</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F102" s="10"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -9461,12 +8855,6 @@
           <t xml:space="preserve">의약품 도매업</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F103" s="10"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -9489,12 +8877,6 @@
           <t xml:space="preserve">의약품 및 의료용품 소매업</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F104" s="10"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -9517,12 +8899,6 @@
           <t xml:space="preserve">그 외 기타 분류 안된 상품 전문 소매업</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F105" s="10"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -9545,12 +8921,6 @@
           <t xml:space="preserve">그 외 기타 무점포 소매업</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F106" s="10"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -9573,12 +8943,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F107" s="10"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -9601,12 +8965,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F108" s="10"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -9629,12 +8987,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F109" s="10"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -9657,12 +9009,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F110" s="10"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -9685,12 +9031,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F111" s="10"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -9713,12 +9053,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F112" s="10"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -9741,12 +9075,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F113" s="10"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -9769,12 +9097,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F114" s="10"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -9797,12 +9119,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F115" s="10"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -9825,12 +9141,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F116" s="10"/>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -9853,12 +9163,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F117" s="10"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -9881,12 +9185,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F118" s="10"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -9909,12 +9207,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F119" s="10"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -9937,12 +9229,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F120" s="10"/>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -9965,12 +9251,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F121" s="10"/>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -9993,12 +9273,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F122" s="10"/>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -10021,12 +9295,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F123" s="10"/>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
@@ -10049,12 +9317,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F124" s="10"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -10077,12 +9339,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F125" s="10"/>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -10105,12 +9361,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F126" s="10"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -10133,12 +9383,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F127" s="10"/>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
@@ -10161,12 +9405,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F128" s="10"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -10189,12 +9427,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F129" s="10"/>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
@@ -10217,12 +9449,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F130" s="10"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="inlineStr">
@@ -10245,12 +9471,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F131" s="10"/>
     </row>
     <row r="132">
       <c r="A132" s="8" t="inlineStr">
@@ -10273,12 +9493,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F132" s="10"/>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -10301,12 +9515,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F133" s="10"/>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
@@ -10329,12 +9537,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F134" s="10"/>
     </row>
     <row r="135">
       <c r="A135" s="8" t="inlineStr">
@@ -10357,12 +9559,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F135" s="10"/>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
@@ -10385,12 +9581,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F136" s="10"/>
     </row>
     <row r="137">
       <c r="A137" s="8" t="inlineStr">
@@ -10413,12 +9603,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F137" s="10"/>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
@@ -10441,12 +9625,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F138" s="10"/>
     </row>
     <row r="139">
       <c r="A139" s="8" t="inlineStr">
@@ -10469,12 +9647,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F139" s="10"/>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
@@ -10497,12 +9669,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F140" s="10"/>
     </row>
     <row r="141">
       <c r="A141" s="8" t="inlineStr">
@@ -10525,12 +9691,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F141" s="10"/>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
@@ -10553,12 +9713,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F142" s="10"/>
     </row>
     <row r="143">
       <c r="A143" s="8" t="inlineStr">
@@ -10581,12 +9735,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F143" s="10"/>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
@@ -10609,12 +9757,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F144" s="10"/>
     </row>
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
@@ -10637,12 +9779,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F145" s="10"/>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
@@ -10665,12 +9801,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F146" s="10"/>
     </row>
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
@@ -10693,12 +9823,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F147" s="10"/>
     </row>
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
@@ -10721,12 +9845,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F148" s="10"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="inlineStr">
@@ -10749,12 +9867,6 @@
           <t xml:space="preserve">의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F149" s="10"/>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
@@ -10777,12 +9889,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F150" s="10"/>
     </row>
     <row r="151">
       <c r="A151" s="8" t="inlineStr">
@@ -10805,12 +9911,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F151" s="10"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
@@ -10833,12 +9933,6 @@
           <t xml:space="preserve">의학 및 약학 연구개발업</t>
         </is>
       </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F152" s="10"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -10861,12 +9955,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F153" s="10"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
@@ -10889,12 +9977,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F154" s="10"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
@@ -10917,12 +9999,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F155" s="10"/>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -10945,12 +10021,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F156" s="10"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
@@ -10973,12 +10043,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F157" s="10"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
@@ -11001,12 +10065,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F158" s="10"/>
     </row>
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
@@ -11029,12 +10087,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F159" s="10"/>
     </row>
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
@@ -11057,12 +10109,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F160" s="10"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -11085,12 +10131,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F161" s="10"/>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
@@ -11113,12 +10153,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F162" s="10"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
@@ -11141,12 +10175,6 @@
           <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F163" s="10"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
@@ -11169,12 +10197,6 @@
           <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
         </is>
       </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F164" s="10"/>
     </row>
     <row r="165">
       <c r="A165" s="8" t="inlineStr">
@@ -11197,12 +10219,6 @@
           <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
         </is>
       </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F165" s="10"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
@@ -11225,12 +10241,6 @@
           <t xml:space="preserve">기타 기술 시험, 검사 및 분석업</t>
         </is>
       </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F166" s="10"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -11253,12 +10263,6 @@
           <t xml:space="preserve">자료 처리업</t>
         </is>
       </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F167" s="10"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
@@ -11281,12 +10285,6 @@
           <t xml:space="preserve">자료 처리업</t>
         </is>
       </c>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F168" s="10"/>
     </row>
     <row r="169">
       <c r="A169" s="8" t="inlineStr">
@@ -11309,12 +10307,6 @@
           <t xml:space="preserve">데이터베이스 및 온라인 정보 제공업</t>
         </is>
       </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F169" s="10"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
@@ -11337,12 +10329,6 @@
           <t xml:space="preserve">컴퓨터 프로그래밍 서비스업</t>
         </is>
       </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F170" s="10"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
@@ -11365,12 +10351,6 @@
           <t xml:space="preserve">응용 소프트웨어 개발 및 공급업</t>
         </is>
       </c>
-      <c r="E171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F171" s="10"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
@@ -11393,12 +10373,6 @@
           <t xml:space="preserve">축산 분뇨 처리업</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F172" s="10"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
@@ -11421,12 +10395,6 @@
           <t xml:space="preserve">지정 외 폐기물 처리업</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F173" s="10"/>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
@@ -11449,12 +10417,6 @@
           <t xml:space="preserve">소독, 구충 및 방제 서비스업</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F174" s="10"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="inlineStr">
@@ -11477,12 +10439,6 @@
           <t xml:space="preserve">작물재배 지원 서비스업</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F175" s="10"/>
     </row>
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
@@ -11505,12 +10461,6 @@
           <t xml:space="preserve">냉장 및 냉동 창고업</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F176" s="10"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
@@ -11533,12 +10483,6 @@
           <t xml:space="preserve">물질 성분 검사 및 분석업</t>
         </is>
       </c>
-      <c r="E177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F177" s="10"/>
     </row>
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
@@ -11561,12 +10505,6 @@
           <t xml:space="preserve">기타 기술 시험, 검사 및 분석업</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F178" s="10"/>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
@@ -11589,12 +10527,6 @@
           <t xml:space="preserve">기타 보관 및 창고업</t>
         </is>
       </c>
-      <c r="E179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F179" s="10"/>
     </row>
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
@@ -11617,16 +10549,10 @@
           <t xml:space="preserve">일반 창고업</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F180" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11640,8 +10566,6 @@
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11672,16 +10596,6 @@
           <t xml:space="preserve">연계 명칭</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -11704,16 +10618,6 @@
           <t xml:space="preserve">종자 및 묘목 생산업</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">씨앗·종근·종균·묘목 생산 — 그린바이오 적용 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -11736,16 +10640,6 @@
           <t xml:space="preserve">육묘업</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210 정의의 육묘 생산 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -11768,16 +10662,6 @@
           <t xml:space="preserve">기타 노지작물 재배업</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대마 전용 세세분류가 없어 기타 작물 컨테이너로 포섭 — 노지재배 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -11800,16 +10684,6 @@
           <t xml:space="preserve">기타 시설작물 재배업</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다 — 시설재배 갈래. 재배 방식에 따라 21190과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -11832,16 +10706,6 @@
           <t xml:space="preserve">음료용 및 향신용 작물 재배업(차 제외)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">향신용 작물의 노지재배 갈래 — 소재 원료용 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -11864,16 +10728,6 @@
           <t xml:space="preserve">인삼 재배업</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소재용 식물의 대표 원료.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -11896,16 +10750,6 @@
           <t xml:space="preserve">약용작물 재배업</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -11928,16 +10772,6 @@
           <t xml:space="preserve">기타 노지작물 재배업</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 소재용 작물의 노지재배 갈래 — 221(대마)과 코드를 공유한다.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -11960,16 +10794,6 @@
           <t xml:space="preserve">음료용 및 향신용 작물 시설재배업</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">향신용 작물의 시설재배 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -11992,16 +10816,6 @@
           <t xml:space="preserve">기타 시설작물 재배업</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 소재용 작물의 시설재배 갈래 — 221(대마)과 코드를 공유한다.</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -12024,16 +10838,6 @@
           <t xml:space="preserve">기타 축산업</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정의가 실험용 쥐·토끼·개 사육을 명시하나 여우·곰·사슴·양잠 등 비실험 축산과 한 코드.</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -12056,16 +10860,6 @@
           <t xml:space="preserve">식용곤충 사육업</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확정안은 곤충 생산 전용 소분류가 없어 290 잔여로 받는다.</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -12088,16 +10882,6 @@
           <t xml:space="preserve">사료용 곤충 사육업</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다(용도: 사료용).</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -12120,16 +10904,6 @@
           <t xml:space="preserve">기타 곤충 사육업</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다. 애완·학습용(22630)은 배제.</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -12152,16 +10926,6 @@
           <t xml:space="preserve">기타 축산업</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환형동물(지렁이 등) 사육 갈래 — 230과 코드 공유(해상도 한계).</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -12184,16 +10948,6 @@
           <t xml:space="preserve">식품용 미생물 제조업</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 자체의 배양·생산 — "식품용" 한정 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -12216,16 +10970,6 @@
           <t xml:space="preserve">그 외 기타 농식품 제조업</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 식물 유래 소재(추출물·농축물 등)의 잔여 컨테이너 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -12248,16 +10992,6 @@
           <t xml:space="preserve">동식물 유래 한약 및 한약제제 제조업</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식물 원형 건조·절단·정제 생약 갈래(동물 유래 일부 혼재).</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -12280,16 +11014,6 @@
           <t xml:space="preserve">식품용 미생물 제조업</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AFSC에서 미생물을 명시한 유일한 제조 코드 — 290(미생물 자체 생산)과 코드를 공유한다(해상도 한계). 미생물 유래 소재의 원료·배양 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -12312,16 +11036,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">효모 제조를 포함하는 컨테이너 — 미생물 유래 효소·발효 소재 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -12344,16 +11058,6 @@
           <t xml:space="preserve">곤충 가공 기타 제품 제조업</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 건조·분쇄·가공 중 소재 갈래(정의는 식용 가공식품에 방점).</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -12376,16 +11080,6 @@
           <t xml:space="preserve">그 외 기타 농식품 제조업</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 컨테이너 포섭 — 비식용 소재는 전용 코드가 없다.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -12408,16 +11102,6 @@
           <t xml:space="preserve">농업용 생물 살균·살충제 및 식물보호제 제조업</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천연 무기화합물까지 포함하는 컨테이너. 11151(화학 농약)은 배제.</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -12440,16 +11124,6 @@
           <t xml:space="preserve">유기질 비료 제조업</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일반 퇴비까지 포괄하는 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -12472,16 +11146,6 @@
           <t xml:space="preserve">축산용 배합사료 제조업</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발효·효소·생물전환 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -12504,16 +11168,6 @@
           <t xml:space="preserve">축산용 단미사료 및 기타 사료 제조업</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다. 조제 보조사료(첨가제 갈래) 포함.</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -12536,16 +11190,6 @@
           <t xml:space="preserve">반려동물용 사료 제조업</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반려동물용 바이오사료 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -12568,16 +11212,6 @@
           <t xml:space="preserve">상토 제조업</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">배지·상토 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -12600,16 +11234,6 @@
           <t xml:space="preserve">그 외 기타 농기자재 제조업</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 농기자재 컨테이너 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -12632,16 +11256,6 @@
           <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화학·천연을 구분하지 않는 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -12664,16 +11278,6 @@
           <t xml:space="preserve">김치류 제조업</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통상 자연발효 다수 — 제어발효 여부 구분 불가.</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -12696,16 +11300,6 @@
           <t xml:space="preserve">장류 제조업</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -12728,16 +11322,6 @@
           <t xml:space="preserve">탁주 및 약주 제조업</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -12760,16 +11344,6 @@
           <t xml:space="preserve">맥아 및 맥주 제조업</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -12792,16 +11366,6 @@
           <t xml:space="preserve">농산물 가공 기타 발효주 제조업</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -12824,16 +11388,6 @@
           <t xml:space="preserve">주정 제조업</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -12856,16 +11410,6 @@
           <t xml:space="preserve">인삼식품 제조업</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -12888,16 +11432,6 @@
           <t xml:space="preserve">건강보조용 액화식품 제조업</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -12920,16 +11454,6 @@
           <t xml:space="preserve">건강 기능식품 제조업</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 활용 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -12952,16 +11476,6 @@
           <t xml:space="preserve">수프 및 균질화식품 제조업</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">균질화식품(영유아식 등) 갈래 포섭 — 환자용 등 나머지는 전용 코드가 없다.</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -12984,16 +11498,6 @@
           <t xml:space="preserve">두부 및 유사 식품 제조업</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식물성 단백 기반 대체식품 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -13016,16 +11520,6 @@
           <t xml:space="preserve">그 외 기타 농식품 제조업</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세포배양·정밀발효 기반은 잔여 컨테이너로 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -13048,16 +11542,6 @@
           <t xml:space="preserve">그 외 기타 농식품 제조업</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 식품 컨테이너 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -13080,16 +11564,6 @@
           <t xml:space="preserve">곤충 가공 기타 제품 제조업</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식용 곤충 완제품 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -13112,16 +11586,6 @@
           <t xml:space="preserve">축산용 의약품 제조업</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물학적 제제와 합성의약품을 구분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -13144,16 +11608,6 @@
           <t xml:space="preserve">반려동물용 의약품 제조업</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다(대상: 반려동물).</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -13176,16 +11630,6 @@
           <t xml:space="preserve">동식물 유래 천연 및 유기농 화장품 제조업</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천연·유기농 표시 일반 화장품까지 포괄하는 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -13208,16 +11652,6 @@
           <t xml:space="preserve">동식물 유래 천연 및 유기농 화장품 제조업</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비누·방향제 등 생활제품 전용 코드가 없어 가장 가까운 동식물 유래 제품 컨테이너로 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -13240,16 +11674,6 @@
           <t xml:space="preserve">동식물 유래 바이오플라스틱 제조업</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동식물 유래 산업제품 컨테이너 — 그린바이오/화이트바이오 경계는 개별 확인.</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -13272,16 +11696,6 @@
           <t xml:space="preserve">동식물 유래 바이오연료 제조업</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -13304,16 +11718,6 @@
           <t xml:space="preserve">종묘 도매업</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종자·묘목 유통 갈래 — 일반 종자 도매가 대부분.</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -13336,16 +11740,6 @@
           <t xml:space="preserve">인삼 및 약용작물 도매업</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소재용 식물 원료 유통 갈래.</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -13368,16 +11762,6 @@
           <t xml:space="preserve">비식용 농축산물 기타 가공품 도매업</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비식용 소재 유통 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -13400,16 +11784,6 @@
           <t xml:space="preserve">작물보호제 도매업</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화학농약을 포함하는 컨테이너 — 바이오농약 취급분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -13432,16 +11806,6 @@
           <t xml:space="preserve">비료 도매업</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화학비료를 포함하는 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -13464,16 +11828,6 @@
           <t xml:space="preserve">사료 도매업</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일반 사료를 포함하는 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -13496,16 +11850,6 @@
           <t xml:space="preserve">그 외 기타 농자재 도매업</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 농자재 도매 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -13528,16 +11872,6 @@
           <t xml:space="preserve">농업 투입재 관련 소매업</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소매 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -13560,16 +11894,6 @@
           <t xml:space="preserve">건강기능식품 도매업</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -13592,16 +11916,6 @@
           <t xml:space="preserve">기타 건강보조식품 소매업</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소매 갈래(인삼류는 43221).</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -13624,16 +11938,6 @@
           <t xml:space="preserve">기타 건강보조식품 소매업</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맞춤형 판매 전용 코드가 없어 소매 컨테이너로 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -13656,16 +11960,6 @@
           <t xml:space="preserve">기타 농산물 가공식품 도매업</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유통전문판매(위탁생산 판매) 형태를 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -13688,16 +11982,6 @@
           <t xml:space="preserve">기타 농산물 가공식품 도매업</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 가공식품 도매 컨테이너.</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -13720,16 +12004,6 @@
           <t xml:space="preserve">기타 식품 소매업</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소매 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -13752,16 +12026,6 @@
           <t xml:space="preserve">동물의약품 도매업</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -13784,16 +12048,6 @@
           <t xml:space="preserve">동물의약품 도매업</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위탁제조판매 형태를 세분하지 않아 441과 코드 공유.</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -13816,16 +12070,6 @@
           <t xml:space="preserve">비식용 농축산물 기타 가공품 도매업</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 유통 컨테이너로 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -13848,16 +12092,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -13880,16 +12114,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -13912,16 +12136,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -13944,16 +12158,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -13976,16 +12180,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -14008,16 +12202,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -14040,16 +12224,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -14072,16 +12246,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -14104,16 +12268,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -14136,16 +12290,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -14168,16 +12312,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -14200,16 +12334,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -14232,16 +12356,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -14264,16 +12378,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -14296,16 +12400,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -14328,16 +12422,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -14360,16 +12444,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -14392,16 +12466,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -14424,16 +12488,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -14456,16 +12510,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -14488,16 +12532,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -14520,16 +12554,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -14552,16 +12576,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -14584,16 +12598,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -14616,16 +12620,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -14648,16 +12642,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -14680,16 +12664,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -14712,16 +12686,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -14744,16 +12708,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합. 82111 정의가 수의학 R&amp;D를 명시적으로 포함한다.</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -14776,16 +12730,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -14808,16 +12752,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합. 82111 정의가 수의학 R&amp;D를 명시적으로 포함한다.</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -14840,16 +12774,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -14872,16 +12796,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -14904,16 +12818,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -14936,16 +12840,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -14968,16 +12862,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -15000,16 +12884,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -15032,16 +12906,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -15064,16 +12928,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -15096,16 +12950,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다. 162는 ICT 기반이 본질이라 이쪽이 주된 대응이다.</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -15128,16 +12972,6 @@
           <t xml:space="preserve">일반 농산업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">관행(비ICT) 방식의 연구개발이 속하는 컨테이너 — 그린바이오 해당분은 부분집합.</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -15160,16 +12994,6 @@
           <t xml:space="preserve">스마트농업 관련 과학기술 연구개발업</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F112" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨단 정보통신기술 기반(디지털육종·유전체 데이터 활용 등)의 연구개발이 속하는 컨테이너 — 같은 소분류라도 연구 방식에 따라 82111과 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -15192,16 +13016,6 @@
           <t xml:space="preserve">일반 농업 데이터 관련 정보서비스업</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일반 농업 데이터 서비스 갈래 — 데이터의 성격(일반/스마트농업)에 따라 84202와 갈린다. 육종 특화 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -15224,16 +13038,6 @@
           <t xml:space="preserve">스마트농업 데이터 관련 정보서비스업</t>
         </is>
       </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F114" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스마트농업 데이터 서비스 갈래 — 위와 같다.</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -15256,16 +13060,6 @@
           <t xml:space="preserve">일반 농업 데이터 관련 정보서비스업</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일반 농업 데이터 서비스 갈래 — 데이터의 성격에 따라 84202와 갈린다.</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -15288,16 +13082,6 @@
           <t xml:space="preserve">스마트농업 데이터 관련 정보서비스업</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스마트농업 데이터 서비스 갈래 — 위와 같다. 521과 코드를 공유한다(해상도 한계).</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
@@ -15320,16 +13104,6 @@
           <t xml:space="preserve">가축 분뇨 처리업</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충·미생물 등 생물학적 처리 여부는 세분하지 않는다.</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -15352,16 +13126,6 @@
           <t xml:space="preserve">음식 폐기물 수집 및 처리업</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">매립·소각 등 비생물적 처리까지 포괄한다.</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -15384,16 +13148,6 @@
           <t xml:space="preserve">일반 농작물 재배 지원 서비스업</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작물 방제 대행 갈래 포섭 — 방제 외 재배 지원 전반을 포괄.</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -15416,16 +13170,6 @@
           <t xml:space="preserve">그 외 기타 축산 관련 서비스업</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="F120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산 방역활동 갈래 포섭.</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
@@ -15448,16 +13192,6 @@
           <t xml:space="preserve">농식품 관련 물질 성분 검사 및 분석, 인증업</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시험·분석·인증 서비스는 확정안에서 590 잔여에 속한다.</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -15480,20 +13214,10 @@
           <t xml:space="preserve">기타 농산업 관련 시험, 검사 및 분석, 인증업</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="F122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15507,8 +13231,6 @@
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="51" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15539,16 +13261,6 @@
           <t xml:space="preserve">연계 명칭</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -15571,16 +13283,6 @@
           <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자·묘목 생산</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -15603,16 +13305,6 @@
           <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전자변형 생물체 생산분</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -15635,16 +13327,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대마가 생명공학 기술 적용 바이오자원 요건을 충족할 때; 계약재배만으로는 부족</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -15667,16 +13349,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소재용 식물이 KS J 바이오자원 요건을 충족할 때; 단순 원료재배는 자동 대응하지 않음</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -15699,16 +13371,6 @@
           <t xml:space="preserve">실험 동물</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실험동물의 사육·증식</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -15731,16 +13393,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충·세포주 등 기타 생물자원</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -15763,16 +13415,6 @@
           <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 미생물·효소 자체를 제품으로 공급할 때</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -15795,16 +13437,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오고분자 식물 유래 소재</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -15827,16 +13459,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 식물 유래 소재</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -15859,16 +13481,6 @@
           <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품첨가물로 제조된 소재</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -15891,16 +13503,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -15923,16 +13525,6 @@
           <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -15955,16 +13547,6 @@
           <t xml:space="preserve">산업용 효소 및 시약류</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산업용 미생물 유래 효소·시약</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -15987,16 +13569,6 @@
           <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 미생물·효소 제품</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -16019,16 +13591,6 @@
           <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 유래 식품첨가물</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -16051,16 +13613,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 소재</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -16083,16 +13635,6 @@
           <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -16115,16 +13657,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 유래 식품소재</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -16147,16 +13679,6 @@
           <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 유래 사료첨가제</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -16179,16 +13701,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 유래 산업용 바이오화학 소재</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -16211,16 +13723,6 @@
           <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -16243,16 +13745,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 바이오화학 소재</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -16275,16 +13767,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잔여 바이오식품 소재</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -16307,16 +13789,6 @@
           <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -16339,16 +13811,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 제조</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -16371,16 +13833,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 제조</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -16403,16 +13855,6 @@
           <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">보조사료·사료첨가제 제조분; 단미사료 제외</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -16435,16 +13877,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생분해성 농업용 필름·용기</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -16467,16 +13899,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -16499,16 +13921,6 @@
           <t xml:space="preserve">바이오 위탁 생산ㆍ대행 서비스</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">타사 의뢰를 받은 바이오제품 제조 대행</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -16531,16 +13943,6 @@
           <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생명공학 기반 식품첨가물 제조</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -16563,16 +13965,6 @@
           <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제어발효 등 바이오 발효식품 제조</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -16595,16 +13987,6 @@
           <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">법정 건강기능식품 제조</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -16627,16 +14009,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -16659,16 +14031,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -16691,16 +14053,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 제품</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -16723,16 +14075,6 @@
           <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오의약품·백신 제조</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -16755,16 +14097,6 @@
           <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오화장품·향장제품 제조</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -16787,16 +14119,6 @@
           <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -16819,16 +14141,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오고분자 생활소재</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -16851,16 +14163,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -16883,16 +14185,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오고분자 산업용 제품</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -16915,16 +14207,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 제품</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -16947,16 +14229,6 @@
           <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오환경 제품에 속하는 잔여범위</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -16979,16 +14251,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원 취급분의 대표 분야; 가공 소재는 실제 품목에 따라 재판정</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -17011,16 +14273,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급품목인 바이오농약의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -17043,16 +14295,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급품목인 바이오비료의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -17075,16 +14317,6 @@
           <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사료첨가제 취급분의 제품 분야; 단미사료 등은 이 코드에 해당하지 않음</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -17107,16 +14339,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 농자재 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -17139,16 +14361,6 @@
           <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급품목인 건강기능식품의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -17171,16 +14383,6 @@
           <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급품목인 맞춤형 건강기능식품의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -17203,16 +14405,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 식품첨가물 등은 실제 품목에 따라 재판정</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -17235,16 +14427,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오식품 취급분의 대표 분야; 실제 품목에 따라 재판정</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -17267,16 +14449,6 @@
           <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급품목인 동물용 바이오의약품의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -17299,16 +14471,6 @@
           <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">참고</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자기 상표로 판매하는 동물용 바이오의약품의 제품 분야</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -17331,16 +14493,6 @@
           <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오제품의 별도 가공·처리·보관 서비스를 수행하는 경우에 한정; 판매 자체는 제외</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -17363,16 +14515,6 @@
           <t xml:space="preserve">종자 및 묘목</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종자·묘목 자체의 개발</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -17395,16 +14537,6 @@
           <t xml:space="preserve">유전자 변형 생물체</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전자변형 생물체 개발분</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -17427,16 +14559,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -17459,16 +14581,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·균주 등 생물자원 자체의 개발</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -17491,16 +14603,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -17523,16 +14625,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 등 생물자원 자체의 개발</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -17555,16 +14647,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -17587,16 +14669,6 @@
           <t xml:space="preserve">기타 바이오자원</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 살아 있는 생물자원에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -17619,16 +14691,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -17651,16 +14713,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·생물학적 방제 제제 개발</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -17683,16 +14735,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -17715,16 +14757,6 @@
           <t xml:space="preserve">바이오농약 및 비료</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·생물학적 비료 제제 개발</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -17747,16 +14779,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -17779,16 +14801,6 @@
           <t xml:space="preserve">사료 첨가제</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사료첨가제 개발분; 단미사료는 제외</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -17811,16 +14823,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -17843,16 +14845,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생분해성 농업용 고분자 자재 개발분</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -17875,16 +14867,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -17907,16 +14889,6 @@
           <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 미생물·효소 소재</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -17939,16 +14911,6 @@
           <t xml:space="preserve">식품 첨가물</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품첨가물로 사용되는 소재</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -17971,16 +14933,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오식품 원료·중간체</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -18003,16 +14955,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -18035,16 +14977,6 @@
           <t xml:space="preserve">건강 기능 식품</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">건강기능식품 제품 개발</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -18067,16 +14999,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -18099,16 +15021,6 @@
           <t xml:space="preserve">식품용 미생물 및 효소</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 미생물·효소 이용기술</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -18131,16 +15043,6 @@
           <t xml:space="preserve">발효 식품</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발효식품 제품기술 개발</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -18163,16 +15065,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -18195,16 +15087,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대체식품 전용 코드가 없어 기타 바이오식품으로 포섭</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -18227,16 +15109,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -18259,16 +15131,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">특수영양·특수의료용도식품 전용 코드가 없음</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -18291,16 +15153,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -18323,16 +15175,6 @@
           <t xml:space="preserve">기타 바이오식품</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F90" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다른 바이오식품 코드에 속하지 않는 산출물</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -18355,16 +15197,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -18387,16 +15219,6 @@
           <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오백신 개발</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -18419,16 +15241,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -18451,16 +15263,6 @@
           <t xml:space="preserve">동물용 바이오의약품</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백신 외 동물용 바이오의약품 개발</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -18483,16 +15285,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 외부 수탁 연구개발</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -18515,16 +15307,6 @@
           <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">핵심</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오화장품·인체용 생활화학제품 개발</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -18547,16 +15329,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -18579,16 +15351,6 @@
           <t xml:space="preserve">바이오화장품 및 생활 화학 제품</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비누·세제 등 바이오 생활화학제품</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -18611,16 +15373,6 @@
           <t xml:space="preserve">바이오 고분자 제품</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오고분자 기반 포장재·생활소재</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -18643,16 +15395,6 @@
           <t xml:space="preserve">기타 바이오화학ㆍ에너지 제품</t>
         </is>
       </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 바이오화학 생활제품</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -18675,16 +15417,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -18707,16 +15439,6 @@
           <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 등 생물학적 환경처리 제제</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -18739,16 +15461,6 @@
           <t xml:space="preserve">환경 처리, 자원 재활용 제제 및 시스템</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">폐자원 처리·재활용 제제와 시스템</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -18771,16 +15483,6 @@
           <t xml:space="preserve">기타 바이오환경 제품 및 서비스</t>
         </is>
       </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경개선 서비스 개발 중 잔여범위</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -18803,16 +15505,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -18835,16 +15527,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">외부 수탁 디지털 기술 연구개발에 한정</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -18867,16 +15549,6 @@
           <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농업생명정보 서비스가 KS J 바이오서비스 범위에 드는 경우; 전용 코드 없음</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -18899,16 +15571,6 @@
           <t xml:space="preserve">기타 연구개발 서비스</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출 분야를 특정하지 못한 외부 수탁 연구개발만 대응</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -18931,16 +15593,6 @@
           <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·단백질 등 생물학적 분석 결과를 고객에게 제공할 때</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -18963,16 +15615,6 @@
           <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F110" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디지털육종 플랫폼이 바이오서비스 잔여범위에 속할 때; 전용 코드 없음</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -18995,16 +15637,6 @@
           <t xml:space="preserve">바이오 분석ㆍ진단 서비스</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·대사체 등 생물학적 분석·진단 서비스</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
@@ -19027,16 +15659,6 @@
           <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F112" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 밖의 생명정보 서비스; 일반 소프트웨어·데이터 판매는 자동 대응하지 않음</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -19059,16 +15681,6 @@
           <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 등 환경처리용 생물 제제를 함께 제공할 때</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -19091,16 +15703,6 @@
           <t xml:space="preserve">환경 처리용 생물 제제 및 시스템</t>
         </is>
       </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F114" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">환경 정화용 생물 제제·시스템 제공분; 순수 방제대행은 별도 코드 없음</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -19123,16 +15725,6 @@
           <t xml:space="preserve">가공 및 처리ㆍ보관 서비스</t>
         </is>
       </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물자원의 특화 처리·보관·수송 서비스</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -19155,20 +15747,10 @@
           <t xml:space="preserve">기타 바이오서비스업</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조건부</t>
-        </is>
-      </c>
-      <c r="F116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시험·분석으로 포섭되지 않는 인증·검사 등 잔여 바이오서비스</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -190,80 +190,62 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="90" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
-    <col min="9" max="9" width="31" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오산업 특수분류(안) 제6차 · 2026. 10. 1.</t>
+          <t xml:space="preserve">그린바이오산업 특수분류(안) 제6차 × KSIC 제11차 · 2026. 10. 1.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">대분류</t>
+          <t xml:space="preserve">대분류 코드</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">대분류명</t>
+          <t xml:space="preserve">대분류 명칭</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">중분류</t>
+          <t xml:space="preserve">중분류 코드</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">중분류명</t>
+          <t xml:space="preserve">중분류 명칭</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">소분류</t>
+          <t xml:space="preserve">소분류 코드</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">소분류명</t>
+          <t xml:space="preserve">소분류 명칭</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">소분류 정의</t>
+          <t xml:space="preserve">KSIC 코드</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">English name</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KSIC11 연계</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AFSC 연계</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KS J 1009 연계</t>
+          <t xml:space="preserve">KSIC 명칭</t>
         </is>
       </c>
     </row>
@@ -298,998 +280,376 @@
           <t xml:space="preserve">그린바이오 종자 생산업</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오가 적용된 종자(증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체 등)를 증식·채종·육묘하여 종자로 생산하는 산업활동을 말한다.</t>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01123</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green-Bio Seed Production</t>
-        </is>
-      </c>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01123, 02011</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21122, 21250</t>
-        </is>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7010, 7020</t>
+          <t xml:space="preserve">종자 및 묘목 생산업</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생산업</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02011</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임업용 종묘 생산업</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 소재용 식물 생산업</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">121</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 소재용 대마 재배업</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대마초(칸나비스 사티바 엘)를 그린바이오 소재의 제조에 원료로 사용하기 위하여 재배·생산하는 산업활동을 말한다. 섬유·종자 채취 목적의 재배는 대마재배자 허가를, 칸나비디올 등 그 밖의 소재 목적의 재배는 규제자유특구의 실증특례 등 별도의 법적 근거를 전제로 한다. 그린바이오 소재 제조와 연결되지 않는 재배는 제외하고, 대마 유래 소재의 추출·가공은 211로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cannabis Cultivation for Green-Bio Materials</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01140</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21190, 21290</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생산업</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">129</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재의 제조에 원료로 사용하기 위하여 대마 외의 식물로서 생명공학 관련 기술이 적용된 것 또는 확인된 그린바이오 제조규격에 따른 식물을 재배·생산하는 산업활동을 말한다. 재배한 식물을 추출·건조·분쇄 등으로 가공하여 소재로 제조하는 활동은 211로 분류한다. 일반 식용·관상용 작물의 재배는 제외한다.</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Production of Other Plants for Green-Bio Materials</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01110, 01121, 01122, 01131, 01132, 01140, 01151, 01159</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21143, 21151, 21152, 21190, 21242, 21290</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생산업</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01110</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곡물 및 기타 식량작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01121</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채소작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01122</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화훼작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01131</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과실작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01132</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음료용 및 향신용 작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01140</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01151</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채소, 화훼 및 과실작물 시설 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01159</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 시설작물 재배업</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 실험동물 생산업</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">130</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 실험동물 생산업</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물실험을 목적으로 사용 또는 사육되는 실험동물을 생물학적 정체성과 증식능력을 유지하면서 사육·증식하여 생산하는 산업활동을 말한다. 동물용 의약품·농자재·식품 등 그린바이오 분야의 연구개발·시험에 공급하는 생산으로 한정하며, 인체용 의약품 개발 등 그린바이오 외 분야에만 공급하는 생산은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Laboratory Animal Production</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01299</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22900</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7030</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생산업</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 축산업</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 생산업</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">190</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 생산업</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는, 농업에 실제적이거나 잠재적인 가치가 있는 미생물·곤충 등 그 밖의 생물자원(농업생물자원)을 그린바이오를 활용하여 생물학적 정체성과 증식능력을 유지하면서 배양·증식·사육하여 생산하는 산업활동을 말한다. 배양·증식한 생물자원을 사멸·건조·분쇄·추출 등으로 가공하여 비증식성 소재로 제조하는 활동은 21의 해당 소분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Production</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299, 21100, 03211, 03212, 03213, 10839</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22610, 22620, 22690, 22900, 31164</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000, 3020</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 제조업</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식물 또는 그 세포·조직배양 산물에서 유래한 물질을 추출·분리·정제·발효·농축·건조·분쇄 등의 방법으로 가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오 소재를 제조하는 산업활동을 말한다. 소재의 유래는 산출물을 기준으로 판정하며, 식물 원료를 배지·영양원으로 삼더라도 산출물이 미생물의 대사산물·균체이면 212로 분류한다. 소재용 식물 자체의 재배는 12의 해당 소분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Plants</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20499, 10839, 20119</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31199, 33910</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010, 2000, 3030, 3000, 8010</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 제조업</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물(농업생물자원)을 배양·발효하거나 그 대사산물·세포성분 등을 분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물(그린바이오 소재)로서 비증식성인 것을 제조하는 산업활동을 말한다. 생물학적 정체성과 증식능력을 유지한 종균·균주 자체의 배양·증식은 190으로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Microorganisms</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21100, 20499, 20119</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31164, 31169</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020, 3020, 3030, 2000, 8010</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 제조업</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충(범위는 413의 정의에 따른다) 또는 그 유래 물질을 건조·분쇄·추출·분리·정제·가공하여 그린바이오제품의 생산에 사용되는 원료 또는 중간생산물인 그린바이오 소재를 제조하는 산업활동을 말한다. 살아 있는 곤충의 사육·증식은 190으로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing of Green-Bio Materials Derived from Insects</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20499, 10839</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33200</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 3050, 2000, 8010</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 제조업</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식물·미생물·곤충 유래 소재로 달리 분류되지 않는 그 밖의 그린바이오 소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 제조하는 산업활동을 말한다. 둘 이상의 유래가 혼합된 소재를 포함한다. 식품첨가물의 제조는 231로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Material Manufacturing</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20499, 21100, 20119, 21220</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31199</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000, 3000, 8010</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 제조업</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약 제조업</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물이나 천연물 등 생물 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biopesticide Manufacturing</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20322</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11152</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 제조업</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오비료 제조업</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">살아 있는 미생물이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료(토양개량용 자재를 포함한다)를 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biofertilizer Manufacturing</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20313</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11133</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 제조업</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물, 천연물 등 생물 유래 물질 또는 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)를 제조하는 산업활동을 말한다. 동물용 의약품은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bio-based Animal Feed Manufacturing</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10902, 10903, 10901, 20119</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11161, 11162, 11163</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3050</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 제조업</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 달리 분류되지 않는 그 밖의 그린바이오 농자재를 제조하는 산업활동을 말한다. 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재의 제조를 포함한다. 종자의 생산은 110으로, 동물용 의약품의 제조는 240으로 분류한다. 농기계·시설·장비와 그린바이오가 기여하지 않는 석유 유래 자재는 제외한다.</t>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Green-Bio Agricultural Input Manufacturing</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20313, 20499</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11140, 11199</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010, 2000, 8010</t>
+          <t xml:space="preserve">그 외 기타 축산업</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 제조업</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여, 식품을 제조·가공·조리하거나 보존하는 과정에서 감미·착색·표백·산화방지 등의 목적으로 식품에 사용되는 식품첨가물을 제조하는 산업활동을 말한다. 식품첨가물이 유래한 생물자원의 종류는 가리지 않으며, 미생물 발효로 생산한 효소·감미료·보존료 등의 제조를 포함한다. 식품첨가물에 해당하지 않는 식품 제조용 원재료·중간생산물의 제조는 21의 해당 소분류로 분류한다.</t>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21100</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green-Bio Food Additive Manufacturing</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10839, 10831, 10832, 20119</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31169</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">기초 의약 물질 제조업</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 제조업</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선별하거나 개량한 특정 미생물·균주를 접종하거나 발효공정 제어기술을 직접 활용하여 발효식품을 제조하는 산업활동을 말한다. 자연발효만을 이용한 일반 발효식품의 제조는 제외한다.</t>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03211</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green-Bio Fermented Food Manufacturing</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10301, 10302, 10309, 10421, 10422, 10831, 10833, 10839, 11111, 11112, 11119, 11121</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31111, 31163, 31211, 31212, 31219, 31221</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">해수면 양식 어업</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 제조업</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 인체에 유용한 기능성을 가진 원료·성분으로 제조한 건강기능식품을 제조하는 산업활동을 말한다. 일반 건강보조식품은 제외한다.</t>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03212</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green-Bio Health Functional Food Manufacturing</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10897, 10895, 10896</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31181, 31182, 31183</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010</t>
+          <t xml:space="preserve">내수면 양식 어업</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 제조업</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 영유아·노인·임산부 등 특정 인구집단의 영양요구를 충족하는 특수영양식품 또는 질병·의학적 상태에 있는 사람의 식사나 영양관리를 위한 특수의료용도식품을 제조하는 산업활동을 말한다.</t>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03213</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manufacturing of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10421, 10893, 10701, 10709, 10892, 10899</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31193</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">수산물 부화 및 수산 종자 생산업</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 제조업</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식물·미생물·곤충과 그 세포배양 산물 등 생물자원·소재 또는 생물공정을 활용하여 기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품을 제조하는 산업활동을 말한다.</t>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green-Bio Alternative Food Manufacturing</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10513, 10519, 10520, 10894, 10899</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31194, 31199</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
         </is>
       </c>
     </row>
@@ -1306,2489 +666,3656 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 소재 제조업</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20499</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20119</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21100</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기초 의약 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20499</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20119</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20499</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20499</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21100</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기초 의약 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20119</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21220</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한의약품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 농자재 제조업</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오농약 제조업</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20322</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물 살균·살충제 및 식물보호제 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오비료 제조업</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20313</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유기질 비료 및 상토 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바이오사료 제조업</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10902</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배합 사료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10903</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단미사료 및 기타 사료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10901</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반려동물용 사료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20119</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20313</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유기질 비료 및 상토 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20499</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 화학제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">23</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품 제조업</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10831</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식초, 발효 및 화학 조미료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10832</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천연 및 혼합 조제 조미료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20119</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기초 유기화학 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10301</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김치류 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10302</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과실 및 그 외 채소 절임식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10309</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 과실·채소 가공 및 저장 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10421</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액상 시유 및 기타 낙농제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10422</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아이스크림 및 기타 식용 빙과류 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10831</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식초, 발효 및 화학 조미료 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10833</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장류 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11111</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">탁주 및 약주 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11112</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">맥아 및 맥주 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11119</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 발효주 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주정 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10897</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건강 기능식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10895</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인삼식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10896</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건강 보조용 액화식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10421</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">액상 시유 및 기타 낙농제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10893</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수프 및 균질화식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10701</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도시락류 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10709</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식사용 가공처리 조리식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10892</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">차류 가공업</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10899</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 식료품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10513</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곡물 혼합 분말 및 반죽 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10519</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 곡물 가공품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10520</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전분제품 및 당류 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10894</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">두부 및 유사 식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10899</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 식료품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">239</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 생물자원·소재 또는 생물공정을 직접 활용하여 그 밖의 식품을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Food Manufacturing</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10309, 10709, 10839, 10899</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31199, 33200</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10309</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 과실·채소 가공 및 저장 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10709</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식사용 가공처리 조리식품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10899</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 식료품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">24</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">240</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F76" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 동물용으로만 사용할 것을 목적으로 하는 의약품과 그 제제를 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Veterinary Medicine Manufacturing</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21230, 21100, 21211</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11171, 11172</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21230</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동물용 의약품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21100</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기초 의약 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21211</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물 의약품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">291</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 향장제품 제조업</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오 소재를 사용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품을 제조하는 산업활동을 말한다. 인체에 직접 사용하지 않는 생활제품은 292로 분류하고, 단순 천연원료 배합제품은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Manufacturing of Green-Bio Cosmetics and Personal Care Products</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20423, 20424</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33920</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20423</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화장품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20424</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표면 광택제 및 실내 가향제 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">292</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생활제품 제조업</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충·천연물 등에서 유래한 그린바이오 소재를 사용하여 생활에 사용하는 물품을 제조하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 제조를 포함한다. 인체에 직접 사용하는 향장제품은 291로, 원단·성형체 등 소재 단계의 제조는 21의 해당 소분류로 분류한다. 단순 천연원료 배합제품은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Household Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20422, 20424, 15190</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33920</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040, 2010, 2000</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제조업</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20422</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치약, 비누 및 기타 세제 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20424</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표면 광택제 및 실내 가향제 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15190</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 가죽제품 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">299</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 직접 활용하여 제조한 그 밖의 그린바이오제품을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Product Manufacturing</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15110, 20203</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33930, 33940</t>
-        </is>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010, 2000, 4000</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15110</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모피 및 가죽 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20203</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">혼성 및 재생 플라스틱 소재 물질 제조업</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 판매·유통업</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">31</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">310</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F86" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종자·종묘·묘목, 종균·균주·세포주, 산업용 곤충 등 살아 있는 생물자원과 추출물·발효물·기능성 원료 등 그린바이오 소재(그린바이오제품의 생산에 사용되는 원료 또는 중간생산물)를 구입하여 사업자 또는 소비자에게 판매하거나, 상품에 대한 소유권을 갖지 않고 수수료·계약에 따라 그 매매를 중개하는 산업활동을 말한다. 자기가 생산한 생물자원·소재의 직접판매는 대분류 1 또는 2의 해당 소분류로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Biological Resource and Material Sales and Distribution</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46202, 46102</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13116, 42230, 42920</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46202</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종자 및 묘목 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="9"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46102</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음·식료품 및 담배 중개업</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 농자재 판매업</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">321</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F88" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오농약 판매업</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농약판매업을 등록한 사업체로서 그린바이오를 활용한 농약을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 화학농약만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biopesticide Sales</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46732</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13113</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 판매업</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비료 및 농약 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">322</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F89" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오비료 판매업</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비료판매업자로서 그린바이오를 활용한 비료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 비료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biofertilizer Sales</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46732</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13112</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 판매업</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비료 및 농약 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">323</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F90" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오사료 판매업</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사료판매업자로서 그린바이오를 활용한 사료를 판매하는 산업활동을 말한다. 생명공학 관련 기술의 적용이 확인되지 않는 일반 사료만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bio-based Animal Feed Sales</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46203</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13114</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3050</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 판매업</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사료 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">329</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 농자재를 판매·유통하는 산업활동을 말한다. 종자의 판매·유통은 310으로, 동물용 의약품의 판매·유통은 34의 해당 소분류로 분류한다. 농기계·시설·장비의 판매와 생명공학 관련 기술의 적용이 확인되지 않는 일반 농자재만을 취급하는 판매업은 제외한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Agricultural Input Sales</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46732, 46203</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13119, 13210</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46732</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비료 및 농약 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46203</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사료 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품 판매업</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">331</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F93" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 판매하는 산업활동을 말한다. 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 활동은 332로, 제조를 위탁하여 자기 상표로 유통하는 활동은 333으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Health Functional Food Sales</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47222, 46443</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42363, 43229</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 판매업</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47222</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건강 보조식품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46443</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화장품 및 화장용품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">332</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 맞춤형건강기능식품판매업</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맞춤형건강기능식품판매업으로서 그린바이오를 활용한 건강기능식품을 개인의 생활습관·건강상태 등에 따라 소분·조합하여 판매하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Customized Green-Bio Health Functional Food Sales</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">47222</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43229</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 판매업</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건강 보조식품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">333</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F96" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용한 식품 또는 식품첨가물을 스스로 제조·가공하지 아니하고 제조업자에게 의뢰하여 제조·가공한 것을 자기 상표로 유통·판매하는 산업활동을 말한다. 식품 유통전문판매업으로서 그린바이오 식품을 취급하는 활동이 이에 해당한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 대분류 2의 해당 제조업으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Specialized Distribution and Sales of Green-Bio Foods</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46443, 46319</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42390</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 판매업</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46443</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화장품 및 화장용품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46319</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 신선 식품 및 단순 가공 식품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">339</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용한 식품과 식품소재를 판매·유통하는 산업활동을 말한다. 식품소재·식품첨가물의 도매와 식품판매업으로서 그린바이오 식품을 취급하는 활동을 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Food Sales</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46311, 46319, 47211, 47219</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42390, 43290</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46311</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과실류 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46319</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 신선 식품 및 단순 가공 식품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47211</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곡물, 곡분 및 가축 사료 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47219</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 신선식품 및 단순 가공식품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 판매·유통업</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">341</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F102" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 도매업</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">허가받은 동물용 의약품 도매상으로서 그린바이오를 활용한 동물용 의약품을 구입하여 사업자에게 판매하거나 그 매매를 중개하는 산업활동을 말한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Veterinary Medicine Wholesale</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46441</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13115</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 판매·유통업</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의약품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">342</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 위탁제조판매업</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 의약품 위탁제조판매업으로서 제조를 위탁하여 만든 그린바이오 동물용 의약품을 자기 상표로 유통·판매하는 산업활동을 말한다. 원재료를 자기계정으로 제공하여 위탁 생산하는 경우는 240으로 분류한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sales of Contract-Manufactured Green-Bio Veterinary Medicines</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46441</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13115</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 판매·유통업</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의약품 도매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">39</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">390</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오를 활용하여 생산된 그린바이오제품을 구입하여 사업자 또는 소비자에게 판매하는 산업활동을 말한다. 그린바이오 향장제품·생활제품의 유통과 동물약국의 그린바이오 동물용 의약품 소매를 포함한다. 취급 재화가 그린바이오 재화인지는 그 재화가 대분류 1 또는 2의 활동으로 생산·제조된 것인지로 판정한다. 그린바이오 재화의 취급 부문과 그 매출을 일반 상품과 분리할 수 있는 경우로 한정하며, 그린바이오 재화가 취급 품목의 일부에 지나지 않아 분리할 수 없는 종합소매·중개플랫폼과 단순 운송·보관은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Sales and Distribution</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47811, 47859, 47999</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42920</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47811</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의약품 및 의료용품 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47859</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 분류 안된 상품 전문 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47999</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 무점포 소매업</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 연구개발업</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">411</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F107" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 종자 연구개발업</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 새로운 종자·품종을 육성하거나 증식용 또는 재배용으로 쓰이는 씨앗·버섯 종균·묘목·포자·영양체의 형질·기능·증식공정·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다. 유전자변형식물체의 품종·형질·안전성 연구개발과 방사선육종·배수체육종·유전체육종·디지털육종 등의 육종을 포함한다.</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Seed Research and Development</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7010, 7020, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">412</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F110" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 재배·사육이나 식품·농자재 생산을 위한 발효에 투입하는 균주·종균 등 살아 있는 미생물 자체를 발굴·개량하거나 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 종자에 해당하는 버섯 종균의 연구개발은 411로 분류한다. 미생물을 이용하여 농자재·식품·의약품 등 산출물을 만드는 연구개발은 그 산출물이 향하는 중분류(42부터 46까지)로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Microorganism Research and Development</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H111" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">413</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F113" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 사육·증식에 투입하는 살아 있는 곤충 자체를 발굴·개량하거나 그 형질·기능·사육공정 또는 이용기술을 연구·개발하는 산업활동을 말한다. 사육·증식의 바탕이 되는 우수 종충(種蟲)의 개발을 포함한다. 여기서 곤충은 사슴벌레·장수풍뎅이·반딧불이·동애등에·꽃무지·뒤영벌, 국제동물명명규약에 따른 분류학상 절지동물문 곤충강에 속하는 동물 전체와 거미류·지네류 등을 포함한다. 사료·식품 등 용도별 산출물을 목적으로 하는 연구개발은 그 산출물이 향하는 중분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Insect Research and Development</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H113" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H115" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">419</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F116" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않으면서 그린바이오를 활용하여, 농업에 실제적이거나 잠재적인 가치가 있는 그 밖의 살아 있는 생물자원(농업생물자원)과 그 형질·기능·증식공정 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research and Development of Other Green-Bio Biological Resources</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">42</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 농자재 연구개발업</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">421</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오농약 연구개발업</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물이나 천연물 등 생물 유래 물질을 활용하여 농작물의 병해충 방제·생육 조절 등에 사용하는 농약과 그 소재·제형·생산공정·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biopesticide Research and Development</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">422</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F122" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오비료 연구개발업</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">살아 있는 미생물이나 그 대사산물을 활용하여 식물 영양 공급과 토양 개량에 사용하는 비료와 그 소재·제형·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 토양개량용 자재·부산물비료 등 토양개량 목적의 미생물 제제 연구개발을 포함한다.</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Biofertilizer Research and Development</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2050, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">423</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F125" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">바이오사료 연구개발업</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충 등 살아 있는 생물, 천연물 등 생물 유래 물질 또는 발효·효소 기술을 활용하여 동물에게 영양을 공급하는 사료(단미사료·배합사료·보조사료)와 그 소재·배합·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 동물용 의약품을 목적으로 하는 연구개발은 44로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bio-based Animal Feed Research and Development</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3050, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">429</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F128" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약·바이오비료·바이오사료로 분류되지 않는 그 밖의 그린바이오 농자재와 그 소재·생산공정 또는 효능을 연구·개발하는 산업활동을 말한다. 생물자원 또는 미생물 발효로 생산한 생분해성 소재를 이용한 농업용 필름·육묘용기, 미생물·천연물을 이용한 축사 환경개선제, 비료·농약에 해당하지 않는 작물 생육 촉진 자재 등의 연구개발을 포함한다. 종자는 411로, 동물용 의약품은 44로 분류한다. 농기계·시설·장비의 연구개발과 그린바이오가 기여하지 않는 석유 유래 자재의 연구개발은 제외한다.</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Agricultural Input Research and Development</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111, 70130</t>
-        </is>
-      </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2010, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="8"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D131" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">431</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F131" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물·곤충·식물 등 살아 있는 생물에서 유래한 천연물 등의 물질을 식품 제조에 사용되는 원재료 또는 중간생산물로 개발하고, 그 성분·기능·추출·분리·정제·표준화·대량생산 또는 이용기술을 연구·개발하는 산업활동을 말한다. 기능성 소재와 그 밖의 식품소재를 모두 포함한다. 대체식품의 소재를 목적으로 하는 연구개발은 434로, 발효공정·미생물 이용기술 자체의 연구개발은 433으로, 향장·생활제품용 소재를 목적으로 하는 연구개발은 45로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Food Ingredient Research and Development</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3020, 3030, 3000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">432</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F134" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 인체에 유용한 기능성을 가진 원료·성분으로 제조한 건강기능식품의 배합·제형·기능성·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 원재료·중간생산물 단계의 연구개발은 431로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Health Functional Food Research and Development</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3010, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H135" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="9"/>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">433</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품의 제조·가공·발효에 사용되는 미생물의 이용기술과 발효공정·효소·안전성 또는 발효식품의 제품기술을 연구·개발하는 산업활동을 말한다. 미생물 균주 자체의 발굴·개량은 412로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research and Development of Green-Bio Fermentation and Microbial Technologies for Food</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3020, 3040, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H137" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="9"/>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H139" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">434</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F140" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 기존 축산물·수산물 등의 식감·풍미·영양 또는 기능을 대체하는 식품과 그 소재·배합·조직화공정·안전성 또는 제품기술을 연구·개발하는 산업활동을 말한다. 식물성·해조류 유래 대체육, 동물세포 배양육, 곤충 대체단백 및 미생물 발효 대체단백의 연구개발을 원료와 방식을 가리지 않고 포함한다.</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Alternative Food Research and Development</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="8"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">435</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F143" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 영유아·노인·임산부 등 특정 인구집단의 영양요구를 충족하는 특수영양식품 또는 질병·의학적 상태에 있는 사람의 식사·영양관리를 위한 특수의료용도식품과 그 소재·배합·제조공정을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research and Development of Green-Bio Special Nutritional Foods and Foods for Special Medical Purposes</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">439</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F146" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 식품과 식품소재를 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Research and Development of Green-Bio Food Ingredients and Products</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H147" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="9"/>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">44</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E149" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">441</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F149" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
         </is>
       </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 동물용으로만 사용할 것을 목적으로 하는 의약품 가운데 동물의 감염병을 예방하기 위한 항원·면역원·백신주·벡터·보조제·제제·생산공정·효능·안전성 또는 투여기술을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bio-based Veterinary Vaccine Research and Development</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70113, 70112, 70111</t>
-        </is>
-      </c>
-      <c r="J53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70113</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="9"/>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="9"/>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H151" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">449</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F152" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
         </is>
       </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업으로 분류되지 않는 그 밖의 그린바이오 동물용 의약품의 후보물질·유효성분·진단제·치료제·제제·생산공정·효능·안전성 또는 이용기술을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Veterinary Medicine Research and Development</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70113, 70112, 70111</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1120, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70113</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의학 및 약학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H153" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="8"/>
+      <c r="F154" s="9"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">45</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 향장·생활제품 연구개발업</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">451</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F155" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 화장품(기능성화장품과 맞춤형화장품을 포함한다)과 인체세정용품·구강용품 등 인체에 직접 사용하는 향장제품, 그리고 그 제조에 사용되는 소재·제형·효능 또는 안전성을 연구·개발하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research and Development of Green-Bio Cosmetics and Personal Care Products</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70130</t>
-        </is>
-      </c>
-      <c r="J55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장·생활제품 연구개발업</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H155" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="9"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="6"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">452</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F157" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오를 활용하여 생활에 사용하는 물품과 그 제조에 사용되는 소재·제형 또는 효능을 연구·개발하는 산업활동을 말한다. 생활공간·섬유·기물의 세정·세탁·탈취·항균·방충에 쓰이는 생활화학제품과, 그린바이오 소재로 만든 가죽 대체재·섬유·포장재·완충재 등 생활용품의 연구개발을 포함한다. 인체에 직접 사용하는 향장제품은 451로, 소재 자체의 연구개발은 431 또는 490으로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Household Product Research and Development</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70130</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2040, 2010, 2000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H157" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="8"/>
+      <c r="F158" s="9"/>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">46</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D159" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 환경·디지털서비스 연구개발업</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E159" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">461</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F159" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원을 이용하여 유기성 폐자원의 처리, 병해충 방제, 축사·농지·농업용수 등 농업환경의 관리·개선에 사용되는 기술·공정 또는 제제를 연구·개발하는 산업활동을 말한다. 농약 제제를 목적으로 하는 연구개발은 421로, 비료·토양개량 제제는 422로, 생물자원 자체의 발굴·개량은 41의 해당 소분류로 분류한다. 환경서비스의 제공 자체는 53의 해당 소분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Environmental Service Research and Development</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70112, 70111</t>
-        </is>
-      </c>
-      <c r="J57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010, 4030, 4000, 8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경·디지털서비스 연구개발업</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H159" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="9"/>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="6"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">462</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F161" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유전체·표현체 등 농업생명자원 데이터의 분석 기술과 디지털육종 플랫폼, 그린바이오 산업용 소프트웨어·인공지능 모델 등 디지털 기술을 연구·개발하는 산업활동을 말한다. 분자표지·유전체 분석을 이용하여 품종 자체를 육성하는 연구개발은 411로, 데이터 서비스의 제공 자체는 52의 해당 소분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Digital Service Research and Development</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70130, 70111</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K58" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040, 8000</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발업</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H161" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="8"/>
+      <c r="F162" s="9"/>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">49</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D163" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E163" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">490</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F163" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 연구개발업</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 연구개발 활동을 말한다. 수요처가 특정되지 않는 다용도 소재·플랫폼 기술의 연구개발을 포함한다. 데이터·디지털 기술의 연구개발은 462로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Research and Development</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70111, 70112, 70130</t>
-        </is>
-      </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82111, 82112</t>
-        </is>
-      </c>
-      <c r="K59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8040</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70111</t>
+        </is>
+      </c>
+      <c r="H163" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물리, 화학 및 생물학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70112</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농림수산학 및 수의학 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="8"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70130</t>
+        </is>
+      </c>
+      <c r="H165" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자연과학 및 공학 융합 연구개발업</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C166" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">52</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D166" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E166" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">521</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F166" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농업생명자원의 유전체 정보 등을 분석하여 디지털육종을 지원하는 유전체·표지·표현체 분석과 생물정보 컨설팅 서비스를 제공하는 산업활동을 말한다. 농림축산식품부가 지정하는 디지털육종 컨설팅·분석 전문기관의 서비스가 이에 해당한다. 품종 자체를 육성하는 연구개발은 411로, 분석 기술·플랫폼 자체의 연구개발은 462로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Digital Breeding Services</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72919, 63111</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84201, 84202</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020, 8000</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72919</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기술 시험, 검사 및 분석업</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="9"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63111</t>
+        </is>
+      </c>
+      <c r="H167" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자료 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">529</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr">
+      <c r="F168" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 소분류에 해당하지 않는 그 밖의 그린바이오 관련 데이터를 수집·분석·가공하여 제공하는 산업활동을 말한다. 생물정보 데이터베이스·플랫폼 운영을 포함한다. 데이터 분석이 새로운 품종·소재·제품·기술의 개발로 이어지는 연구개발은 대분류 4의 해당 소분류로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Information and Data Services</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63111, 63991, 62010, 58222</t>
-        </is>
-      </c>
-      <c r="J61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84201, 84202</t>
-        </is>
-      </c>
-      <c r="K61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8020, 8000</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63111</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자료 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63991</t>
+        </is>
+      </c>
+      <c r="H169" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터베이스 및 온라인 정보 제공업</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="8"/>
+      <c r="F170" s="9"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62010</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컴퓨터 프로그래밍 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="8"/>
+      <c r="F171" s="9"/>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58222</t>
+        </is>
+      </c>
+      <c r="H171" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응용 소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">53</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D172" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 환경서비스업</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E172" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">531</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F172" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충·미생물 등 살아 있는 생물자원에 생명공학 관련 기술을 적용하여 가축분뇨·음식물류 폐기물 등 농업계 유기성 폐자원을 분해·처리하는 산업활동을 말한다. 처리 수수료가 주된 수입인 경우에 적용하며, 처리 과정에서 생산한 유충 사료의 제조는 223으로, 분변토 비료의 제조는 222로 분류한다.</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Organic Waste Resource Treatment</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37022, 38210</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89112, 89120</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스업</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37022</t>
+        </is>
+      </c>
+      <c r="H172" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산 분뇨 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="8"/>
+      <c r="F173" s="9"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38210</t>
+        </is>
+      </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정 외 폐기물 처리업</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">532</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F174" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천적곤충·미생물 등 살아 있는 생물자원을 핵심 수단으로 삼아, 생명공학 관련 기술과 그 생물학적 특성에 기반한 프로그램을 설계·수행함으로써 농작물의 병해충을 방제하거나 축사·농지·농업용수의 환경을 관리·개선하는 산업활동을 말한다. 방제업 가운데 천적·미생물을 이용하는 생물적 방제를 포함한다. 구입한 바이오농약·환경개선제를 생물학적 설계 없이 단순 살포·시공하는 대행, 화학농약만을 사용하는 방제, 농업과 관련되지 않는 일반 산업폐수·오염토양의 정화는 제외한다.</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Green-Bio Pest Control and Agricultural Environment Management</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74220, 01411</t>
-        </is>
-      </c>
-      <c r="J63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24111, 24299</t>
-        </is>
-      </c>
-      <c r="K63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4010</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 정보·환경 및 기타 서비스업</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74220</t>
+        </is>
+      </c>
+      <c r="H174" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소독, 구충 및 방제 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="9"/>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01411</t>
+        </is>
+      </c>
+      <c r="H175" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작물재배 지원 서비스업</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">59</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">590</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F176" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">기타 그린바이오 서비스업</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앞의 중분류에 해당하지 않는 그 밖의 그린바이오 관련 서비스를 제공하는 산업활동을 말한다. 종자·미생물·곤충·천연물·식품·동물용 의약품 등 그린바이오 재화의 품질·성분·기능성·안전성·유효성을 정형화된 방법으로 시험·검정·분석하는 서비스(종자 검정, 미생물 동정, 유전자·성분 분석과 동물용 의약품의 비임상 시험 수탁), 그린바이오 재화 또는 그 생산·제조 공정이 법령·규격·표준에 적합한지를 검사·심사하여 인증하는 서비스, 종자·균주 등 생물자원의 정체성 유지에 특화된 보관·수송 서비스를 포함한다. 새로운 품종·소재·제품·기술의 개발을 목적으로 하는 수탁 연구는 대분류 4의 해당 소분류로, 디지털육종을 지원하는 유전체·생물정보 분석 서비스는 521로 분류한다. 단순 운송·보관은 제외하고, 그린바이오 기술에 관한 교육·훈련은 생명공학 기술을 적용하는 활동이 아니라 지식을 전달하는 활동이므로 제외한다(산업활동이 아닌 인력양성 지원체계에 속한다).</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Green-Bio Services</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52102, 72911, 72919, 52109, 52101</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89401, 89409</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8050, 8000</t>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52102</t>
+        </is>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냉장 및 냉동 창고업</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="8"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72911</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물질 성분 검사 및 분석업</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="8"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72919</t>
+        </is>
+      </c>
+      <c r="H178" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 기술 시험, 검사 및 분석업</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="8"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52109</t>
+        </is>
+      </c>
+      <c r="H179" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 보관 및 창고업</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="8"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52101</t>
+        </is>
+      </c>
+      <c r="H180" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일반 창고업</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="C17:C22"/>
-    <mergeCell ref="D17:D22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="A9:A26"/>
-    <mergeCell ref="B9:B26"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="D32:D35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="A27:A38"/>
-    <mergeCell ref="B27:B38"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="C47:C52"/>
-    <mergeCell ref="D47:D52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="A39:A59"/>
-    <mergeCell ref="B39:B59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="B60:B64"/>
+  <mergeCells count="159">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="F7:F14"/>
+    <mergeCell ref="C6:C14"/>
+    <mergeCell ref="D6:D14"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="B4:B21"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="C22:C33"/>
+    <mergeCell ref="D22:D33"/>
+    <mergeCell ref="E36:E39"/>
+    <mergeCell ref="F36:F39"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="C34:C41"/>
+    <mergeCell ref="D34:D41"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="E46:E57"/>
+    <mergeCell ref="F46:F57"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="F58:F60"/>
+    <mergeCell ref="E61:E66"/>
+    <mergeCell ref="F61:F66"/>
+    <mergeCell ref="E67:E71"/>
+    <mergeCell ref="F67:F71"/>
+    <mergeCell ref="E72:E75"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="C42:C75"/>
+    <mergeCell ref="D42:D75"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="E81:E83"/>
+    <mergeCell ref="F81:F83"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="C79:C85"/>
+    <mergeCell ref="D79:D85"/>
+    <mergeCell ref="A22:A85"/>
+    <mergeCell ref="B22:B85"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="D88:D92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="C93:C101"/>
+    <mergeCell ref="D93:D101"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E104:E106"/>
+    <mergeCell ref="F104:F106"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="A86:A106"/>
+    <mergeCell ref="B86:B106"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="F107:F109"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="F110:F112"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="F113:F115"/>
+    <mergeCell ref="E116:E118"/>
+    <mergeCell ref="F116:F118"/>
+    <mergeCell ref="C107:C118"/>
+    <mergeCell ref="D107:D118"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="F119:F121"/>
+    <mergeCell ref="E122:E124"/>
+    <mergeCell ref="F122:F124"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="F125:F127"/>
+    <mergeCell ref="E128:E130"/>
+    <mergeCell ref="F128:F130"/>
+    <mergeCell ref="C119:C130"/>
+    <mergeCell ref="D119:D130"/>
+    <mergeCell ref="E131:E133"/>
+    <mergeCell ref="F131:F133"/>
+    <mergeCell ref="E134:E136"/>
+    <mergeCell ref="F134:F136"/>
+    <mergeCell ref="E137:E139"/>
+    <mergeCell ref="F137:F139"/>
+    <mergeCell ref="E140:E142"/>
+    <mergeCell ref="F140:F142"/>
+    <mergeCell ref="E143:E145"/>
+    <mergeCell ref="F143:F145"/>
+    <mergeCell ref="E146:E148"/>
+    <mergeCell ref="F146:F148"/>
+    <mergeCell ref="C131:C148"/>
+    <mergeCell ref="D131:D148"/>
+    <mergeCell ref="E149:E151"/>
+    <mergeCell ref="F149:F151"/>
+    <mergeCell ref="E152:E154"/>
+    <mergeCell ref="F152:F154"/>
+    <mergeCell ref="C149:C154"/>
+    <mergeCell ref="D149:D154"/>
+    <mergeCell ref="E155:E156"/>
+    <mergeCell ref="F155:F156"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="F157:F158"/>
+    <mergeCell ref="C155:C158"/>
+    <mergeCell ref="D155:D158"/>
+    <mergeCell ref="E159:E160"/>
+    <mergeCell ref="F159:F160"/>
+    <mergeCell ref="E161:E162"/>
+    <mergeCell ref="F161:F162"/>
+    <mergeCell ref="C159:C162"/>
+    <mergeCell ref="D159:D162"/>
+    <mergeCell ref="E163:E165"/>
+    <mergeCell ref="F163:F165"/>
+    <mergeCell ref="C163:C165"/>
+    <mergeCell ref="D163:D165"/>
+    <mergeCell ref="A107:A165"/>
+    <mergeCell ref="B107:B165"/>
+    <mergeCell ref="E166:E167"/>
+    <mergeCell ref="F166:F167"/>
+    <mergeCell ref="E168:E171"/>
+    <mergeCell ref="F168:F171"/>
+    <mergeCell ref="C166:C171"/>
+    <mergeCell ref="D166:D171"/>
+    <mergeCell ref="E172:E173"/>
+    <mergeCell ref="F172:F173"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="C172:C175"/>
+    <mergeCell ref="D172:D175"/>
+    <mergeCell ref="E176:E180"/>
+    <mergeCell ref="F176:F180"/>
+    <mergeCell ref="C176:C180"/>
+    <mergeCell ref="D176:D180"/>
+    <mergeCell ref="A166:A180"/>
+    <mergeCell ref="B166:B180"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/xlsx/그린바이오산업_특수분류표_6차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_6차.xlsx
@@ -7206,16 +7206,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 생산업</t>
-        </is>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">02011</t>
@@ -7272,16 +7264,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01121</t>
@@ -7294,16 +7278,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01122</t>
@@ -7316,16 +7292,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01131</t>
@@ -7338,16 +7306,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01132</t>
@@ -7360,16 +7320,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01140</t>
@@ -7382,16 +7334,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01151</t>
@@ -7404,16 +7348,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01159</t>
@@ -7470,16 +7406,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21100</t>
@@ -7492,16 +7420,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">03211</t>
@@ -7514,16 +7434,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">03212</t>
@@ -7536,16 +7448,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">03213</t>
@@ -7558,16 +7462,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A21" s="8"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10839</t>
@@ -7602,16 +7498,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A23" s="8"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10839</t>
@@ -7624,16 +7512,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A24" s="8"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20119</t>
@@ -7668,16 +7548,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A26" s="8"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20499</t>
@@ -7690,16 +7562,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A27" s="8"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20119</t>
@@ -7734,16 +7598,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A29" s="8"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10839</t>
@@ -7778,16 +7634,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A31" s="8"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21100</t>
@@ -7800,16 +7648,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A32" s="8"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20119</t>
@@ -7822,16 +7662,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A33" s="8"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21220</t>
@@ -7910,16 +7742,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
+      <c r="A37" s="8"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10903</t>
@@ -7932,16 +7756,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
+      <c r="A38" s="8"/>
+      <c r="B38" s="10"/>
       <c r="C38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10901</t>
@@ -7954,16 +7770,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
+      <c r="A39" s="8"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20119</t>
@@ -7998,16 +7806,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
-        </is>
-      </c>
+      <c r="A41" s="8"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20499</t>
@@ -8042,16 +7842,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
-        </is>
-      </c>
+      <c r="A43" s="8"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10831</t>
@@ -8064,16 +7856,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
-        </is>
-      </c>
+      <c r="A44" s="8"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10832</t>
@@ -8086,16 +7870,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품첨가물 제조업</t>
-        </is>
-      </c>
+      <c r="A45" s="8"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20119</t>
@@ -8130,16 +7906,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A47" s="8"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10302</t>
@@ -8152,16 +7920,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A48" s="8"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10309</t>
@@ -8174,16 +7934,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A49" s="8"/>
+      <c r="B49" s="10"/>
       <c r="C49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10421</t>
@@ -8196,16 +7948,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A50" s="8"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10422</t>
@@ -8218,16 +7962,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A51" s="8"/>
+      <c r="B51" s="10"/>
       <c r="C51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10831</t>
@@ -8240,16 +7976,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A52" s="8"/>
+      <c r="B52" s="10"/>
       <c r="C52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10833</t>
@@ -8262,16 +7990,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A53" s="8"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10839</t>
@@ -8284,16 +8004,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A54" s="8"/>
+      <c r="B54" s="10"/>
       <c r="C54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11111</t>
@@ -8306,16 +8018,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A55" s="8"/>
+      <c r="B55" s="10"/>
       <c r="C55" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11112</t>
@@ -8328,16 +8032,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A56" s="8"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11119</t>
@@ -8350,16 +8046,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A57" s="8"/>
+      <c r="B57" s="10"/>
       <c r="C57" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11121</t>
@@ -8394,16 +8082,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
+      <c r="A59" s="8"/>
+      <c r="B59" s="10"/>
       <c r="C59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10895</t>
@@ -8416,16 +8096,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
+      <c r="A60" s="8"/>
+      <c r="B60" s="10"/>
       <c r="C60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10896</t>
@@ -8460,16 +8132,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
+      <c r="A62" s="8"/>
+      <c r="B62" s="10"/>
       <c r="C62" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10893</t>
@@ -8482,16 +8146,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
+      <c r="A63" s="8"/>
+      <c r="B63" s="10"/>
       <c r="C63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10701</t>
@@ -8504,16 +8160,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
+      <c r="A64" s="8"/>
+      <c r="B64" s="10"/>
       <c r="C64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10709</t>
@@ -8526,16 +8174,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
+      <c r="A65" s="8"/>
+      <c r="B65" s="10"/>
       <c r="C65" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10892</t>
@@ -8548,16 +8188,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
-        </is>
-      </c>
+      <c r="A66" s="8"/>
+      <c r="B66" s="10"/>
       <c r="C66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10899</t>
@@ -8592,16 +8224,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
+      <c r="A68" s="8"/>
+      <c r="B68" s="10"/>
       <c r="C68" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10519</t>
@@ -8614,16 +8238,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
+      <c r="A69" s="8"/>
+      <c r="B69" s="10"/>
       <c r="C69" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10520</t>
@@ -8636,16 +8252,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
+      <c r="A70" s="8"/>
+      <c r="B70" s="10"/>
       <c r="C70" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10894</t>
@@ -8658,16 +8266,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
+      <c r="A71" s="8"/>
+      <c r="B71" s="10"/>
       <c r="C71" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10899</t>
@@ -8702,16 +8302,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
-        </is>
-      </c>
+      <c r="A73" s="8"/>
+      <c r="B73" s="10"/>
       <c r="C73" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10709</t>
@@ -8724,16 +8316,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
-        </is>
-      </c>
+      <c r="A74" s="8"/>
+      <c r="B74" s="10"/>
       <c r="C74" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10839</t>
@@ -8746,16 +8330,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
-        </is>
-      </c>
+      <c r="A75" s="8"/>
+      <c r="B75" s="10"/>
       <c r="C75" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">10899</t>
@@ -8790,16 +8366,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
+      <c r="A77" s="8"/>
+      <c r="B77" s="10"/>
       <c r="C77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21100</t>
@@ -8812,16 +8380,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
+      <c r="A78" s="8"/>
+      <c r="B78" s="10"/>
       <c r="C78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21211</t>
@@ -8856,16 +8416,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 제조업</t>
-        </is>
-      </c>
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
       <c r="C80" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20424</t>
@@ -8900,16 +8452,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
-        </is>
-      </c>
+      <c r="A82" s="8"/>
+      <c r="B82" s="10"/>
       <c r="C82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20424</t>
@@ -8922,16 +8466,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
-        </is>
-      </c>
+      <c r="A83" s="8"/>
+      <c r="B83" s="10"/>
       <c r="C83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">15190</t>
@@ -8966,16 +8502,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
+      <c r="A85" s="8"/>
+      <c r="B85" s="10"/>
       <c r="C85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">20203</t>
@@ -9010,16 +8538,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
-        </is>
-      </c>
+      <c r="A87" s="8"/>
+      <c r="B87" s="10"/>
       <c r="C87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46102</t>
@@ -9120,16 +8640,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
-        </is>
-      </c>
+      <c r="A92" s="8"/>
+      <c r="B92" s="10"/>
       <c r="C92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46203</t>
@@ -9164,16 +8676,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
-        </is>
-      </c>
+      <c r="A94" s="8"/>
+      <c r="B94" s="10"/>
       <c r="C94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46443</t>
@@ -9230,16 +8734,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품 유통전문판매업</t>
-        </is>
-      </c>
+      <c r="A97" s="8"/>
+      <c r="B97" s="10"/>
       <c r="C97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46319</t>
@@ -9274,16 +8770,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
-        </is>
-      </c>
+      <c r="A99" s="8"/>
+      <c r="B99" s="10"/>
       <c r="C99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">46319</t>
@@ -9296,16 +8784,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
-        </is>
-      </c>
+      <c r="A100" s="8"/>
+      <c r="B100" s="10"/>
       <c r="C100" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">47211</t>
@@ -9318,16 +8798,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339</t>
-        </is>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
-        </is>
-      </c>
+      <c r="A101" s="8"/>
+      <c r="B101" s="10"/>
       <c r="C101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">47219</t>
@@ -9406,16 +8878,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390</t>
-        </is>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
-        </is>
-      </c>
+      <c r="A105" s="8"/>
+      <c r="B105" s="10"/>
       <c r="C105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">47859</t>
@@ -9428,16 +8892,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">390</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 판매·유통업</t>
-        </is>
-      </c>
+      <c r="A106" s="8"/>
+      <c r="B106" s="10"/>
       <c r="C106" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">47999</t>
@@ -9472,16 +8928,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
-        </is>
-      </c>
+      <c r="A108" s="8"/>
+      <c r="B108" s="10"/>
       <c r="C108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9494,16 +8942,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
-        </is>
-      </c>
+      <c r="A109" s="8"/>
+      <c r="B109" s="10"/>
       <c r="C109" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9538,16 +8978,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
-        </is>
-      </c>
+      <c r="A111" s="8"/>
+      <c r="B111" s="10"/>
       <c r="C111" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9560,16 +8992,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
-        </is>
-      </c>
+      <c r="A112" s="8"/>
+      <c r="B112" s="10"/>
       <c r="C112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9604,16 +9028,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
-        </is>
-      </c>
+      <c r="A114" s="8"/>
+      <c r="B114" s="10"/>
       <c r="C114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9626,16 +9042,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
-        </is>
-      </c>
+      <c r="A115" s="8"/>
+      <c r="B115" s="10"/>
       <c r="C115" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9670,16 +9078,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
+      <c r="A117" s="8"/>
+      <c r="B117" s="10"/>
       <c r="C117" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9692,16 +9092,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
+      <c r="A118" s="8"/>
+      <c r="B118" s="10"/>
       <c r="C118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9736,16 +9128,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
-        </is>
-      </c>
+      <c r="A120" s="8"/>
+      <c r="B120" s="10"/>
       <c r="C120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9758,16 +9142,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
-        </is>
-      </c>
+      <c r="A121" s="8"/>
+      <c r="B121" s="10"/>
       <c r="C121" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9802,16 +9178,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A123" s="8"/>
+      <c r="B123" s="10"/>
       <c r="C123" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9824,16 +9192,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A124" s="8"/>
+      <c r="B124" s="10"/>
       <c r="C124" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9868,16 +9228,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">423</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A126" s="8"/>
+      <c r="B126" s="10"/>
       <c r="C126" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9890,16 +9242,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">423</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A127" s="8"/>
+      <c r="B127" s="10"/>
       <c r="C127" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -9934,16 +9278,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A129" s="8"/>
+      <c r="B129" s="10"/>
       <c r="C129" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -9956,16 +9292,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A130" s="8"/>
+      <c r="B130" s="10"/>
       <c r="C130" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10000,16 +9328,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A132" s="8"/>
+      <c r="B132" s="10"/>
       <c r="C132" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10022,16 +9342,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A133" s="8"/>
+      <c r="B133" s="10"/>
       <c r="C133" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10066,16 +9378,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A135" s="8"/>
+      <c r="B135" s="10"/>
       <c r="C135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10088,16 +9392,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A136" s="8"/>
+      <c r="B136" s="10"/>
       <c r="C136" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10132,16 +9428,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">433</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
-        </is>
-      </c>
+      <c r="A138" s="8"/>
+      <c r="B138" s="10"/>
       <c r="C138" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10154,16 +9442,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">433</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
-        </is>
-      </c>
+      <c r="A139" s="8"/>
+      <c r="B139" s="10"/>
       <c r="C139" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10198,16 +9478,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A141" s="8"/>
+      <c r="B141" s="10"/>
       <c r="C141" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10220,16 +9492,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A142" s="8"/>
+      <c r="B142" s="10"/>
       <c r="C142" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10264,16 +9528,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">435</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A144" s="8"/>
+      <c r="B144" s="10"/>
       <c r="C144" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10286,16 +9542,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">435</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A145" s="8"/>
+      <c r="B145" s="10"/>
       <c r="C145" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10330,16 +9578,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439</t>
-        </is>
-      </c>
-      <c r="B147" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A147" s="8"/>
+      <c r="B147" s="10"/>
       <c r="C147" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10352,16 +9592,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439</t>
-        </is>
-      </c>
-      <c r="B148" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A148" s="8"/>
+      <c r="B148" s="10"/>
       <c r="C148" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10396,16 +9628,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">441</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
-        </is>
-      </c>
+      <c r="A150" s="8"/>
+      <c r="B150" s="10"/>
       <c r="C150" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10418,16 +9642,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">441</t>
-        </is>
-      </c>
-      <c r="B151" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
-        </is>
-      </c>
+      <c r="A151" s="8"/>
+      <c r="B151" s="10"/>
       <c r="C151" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -10462,16 +9678,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A153" s="8"/>
+      <c r="B153" s="10"/>
       <c r="C153" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10484,16 +9692,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A154" s="8"/>
+      <c r="B154" s="10"/>
       <c r="C154" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -10528,16 +9728,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A156" s="8"/>
+      <c r="B156" s="10"/>
       <c r="C156" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10572,16 +9764,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B158" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A158" s="8"/>
+      <c r="B158" s="10"/>
       <c r="C158" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10616,16 +9800,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A160" s="8"/>
+      <c r="B160" s="10"/>
       <c r="C160" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -10660,16 +9836,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462</t>
-        </is>
-      </c>
-      <c r="B162" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A162" s="8"/>
+      <c r="B162" s="10"/>
       <c r="C162" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70111</t>
@@ -10704,16 +9872,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490</t>
-        </is>
-      </c>
-      <c r="B164" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
-        </is>
-      </c>
+      <c r="A164" s="8"/>
+      <c r="B164" s="10"/>
       <c r="C164" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70112</t>
@@ -10726,16 +9886,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490</t>
-        </is>
-      </c>
-      <c r="B165" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
-        </is>
-      </c>
+      <c r="A165" s="8"/>
+      <c r="B165" s="10"/>
       <c r="C165" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70130</t>
@@ -10770,16 +9922,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
-        </is>
-      </c>
+      <c r="A167" s="8"/>
+      <c r="B167" s="10"/>
       <c r="C167" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">63111</t>
@@ -10814,16 +9958,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B169" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
+      <c r="A169" s="8"/>
+      <c r="B169" s="10"/>
       <c r="C169" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">63991</t>
@@ -10836,16 +9972,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B170" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
+      <c r="A170" s="8"/>
+      <c r="B170" s="10"/>
       <c r="C170" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">62010</t>
@@ -10858,16 +9986,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B171" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
+      <c r="A171" s="8"/>
+      <c r="B171" s="10"/>
       <c r="C171" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">58222</t>
@@ -10902,16 +10022,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">531</t>
-        </is>
-      </c>
-      <c r="B173" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
-        </is>
-      </c>
+      <c r="A173" s="8"/>
+      <c r="B173" s="10"/>
       <c r="C173" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">38210</t>
@@ -10946,16 +10058,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532</t>
-        </is>
-      </c>
-      <c r="B175" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
-        </is>
-      </c>
+      <c r="A175" s="8"/>
+      <c r="B175" s="10"/>
       <c r="C175" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">01411</t>
@@ -10990,16 +10094,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B177" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A177" s="8"/>
+      <c r="B177" s="10"/>
       <c r="C177" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">72911</t>
@@ -11012,16 +10108,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B178" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A178" s="8"/>
+      <c r="B178" s="10"/>
       <c r="C178" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">72919</t>
@@ -11034,16 +10122,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B179" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A179" s="8"/>
+      <c r="B179" s="10"/>
       <c r="C179" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">52109</t>
@@ -11056,16 +10136,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B180" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A180" s="8"/>
+      <c r="B180" s="10"/>
       <c r="C180" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">52101</t>
@@ -11078,8 +10150,110 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="103">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A46:A57"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A61:A66"/>
+    <mergeCell ref="B61:B66"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="A81:A83"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:B133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="B134:B136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="B140:B142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="B143:B145"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="B146:B148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="B149:B151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="A163:A165"/>
+    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="A168:A171"/>
+    <mergeCell ref="B168:B171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="A176:A180"/>
+    <mergeCell ref="B176:B180"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11147,16 +10321,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 생산업</t>
-        </is>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21250</t>
@@ -11191,16 +10357,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재용 대마 재배업</t>
-        </is>
-      </c>
+      <c r="A7" s="8"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21290</t>
@@ -11235,16 +10393,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21151</t>
@@ -11257,16 +10407,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21152</t>
@@ -11279,16 +10421,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21190</t>
@@ -11301,16 +10435,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21242</t>
@@ -11323,16 +10449,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재용 식물 생산업</t>
-        </is>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">21290</t>
@@ -11389,16 +10507,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">22620</t>
@@ -11411,16 +10521,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">22690</t>
@@ -11433,16 +10535,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">22900</t>
@@ -11455,16 +10549,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31164</t>
@@ -11499,16 +10585,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A21" s="8"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">33910</t>
@@ -11543,16 +10621,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A23" s="8"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31169</t>
@@ -11675,16 +10745,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
+      <c r="A29" s="8"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11162</t>
@@ -11697,16 +10759,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 제조업</t>
-        </is>
-      </c>
+      <c r="A30" s="8"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11163</t>
@@ -11741,16 +10795,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
-        </is>
-      </c>
+      <c r="A32" s="8"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11199</t>
@@ -11807,16 +10853,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A35" s="8"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31163</t>
@@ -11829,16 +10867,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A36" s="8"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31211</t>
@@ -11851,16 +10881,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A37" s="8"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31212</t>
@@ -11873,16 +10895,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A38" s="8"/>
+      <c r="B38" s="10"/>
       <c r="C38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31219</t>
@@ -11895,16 +10909,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
+      <c r="A39" s="8"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31221</t>
@@ -11939,16 +10945,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
+      <c r="A41" s="8"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31182</t>
@@ -11961,16 +10959,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
+      <c r="A42" s="8"/>
+      <c r="B42" s="10"/>
       <c r="C42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31183</t>
@@ -12027,16 +11017,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
-        </is>
-      </c>
+      <c r="A45" s="8"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">31199</t>
@@ -12071,16 +11053,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
-        </is>
-      </c>
+      <c r="A47" s="8"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">33200</t>
@@ -12115,16 +11089,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
+      <c r="A49" s="8"/>
+      <c r="B49" s="10"/>
       <c r="C49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">11172</t>
@@ -12203,16 +11169,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
+      <c r="A53" s="8"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">33940</t>
@@ -12247,16 +11205,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
-        </is>
-      </c>
+      <c r="A55" s="8"/>
+      <c r="B55" s="10"/>
       <c r="C55" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">42230</t>
@@ -12269,16 +11219,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·소재 판매·유통업</t>
-        </is>
-      </c>
+      <c r="A56" s="8"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">42920</t>
@@ -12379,16 +11321,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 판매업</t>
-        </is>
-      </c>
+      <c r="A61" s="8"/>
+      <c r="B61" s="10"/>
       <c r="C61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">13210</t>
@@ -12423,16 +11357,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품판매업</t>
-        </is>
-      </c>
+      <c r="A63" s="8"/>
+      <c r="B63" s="10"/>
       <c r="C63" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">43229</t>
@@ -12511,16 +11437,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">339</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품 판매업</t>
-        </is>
-      </c>
+      <c r="A67" s="8"/>
+      <c r="B67" s="10"/>
       <c r="C67" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">43290</t>
@@ -12621,16 +11539,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
-        </is>
-      </c>
+      <c r="A72" s="8"/>
+      <c r="B72" s="10"/>
       <c r="C72" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12665,16 +11575,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
-        </is>
-      </c>
+      <c r="A74" s="8"/>
+      <c r="B74" s="10"/>
       <c r="C74" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12709,16 +11611,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
-        </is>
-      </c>
+      <c r="A76" s="8"/>
+      <c r="B76" s="10"/>
       <c r="C76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12753,16 +11647,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
+      <c r="A78" s="8"/>
+      <c r="B78" s="10"/>
       <c r="C78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12797,16 +11683,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
-        </is>
-      </c>
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
       <c r="C80" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12841,16 +11719,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A82" s="8"/>
+      <c r="B82" s="10"/>
       <c r="C82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12885,16 +11755,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">423</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A84" s="8"/>
+      <c r="B84" s="10"/>
       <c r="C84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12929,16 +11791,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A86" s="8"/>
+      <c r="B86" s="10"/>
       <c r="C86" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -12973,16 +11827,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A88" s="8"/>
+      <c r="B88" s="10"/>
       <c r="C88" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13017,16 +11863,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A90" s="8"/>
+      <c r="B90" s="10"/>
       <c r="C90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13061,16 +11899,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">433</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
-        </is>
-      </c>
+      <c r="A92" s="8"/>
+      <c r="B92" s="10"/>
       <c r="C92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13105,16 +11935,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A94" s="8"/>
+      <c r="B94" s="10"/>
       <c r="C94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13149,16 +11971,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">435</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A96" s="8"/>
+      <c r="B96" s="10"/>
       <c r="C96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13193,16 +12007,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A98" s="8"/>
+      <c r="B98" s="10"/>
       <c r="C98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13237,16 +12043,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">441</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
-        </is>
-      </c>
+      <c r="A100" s="8"/>
+      <c r="B100" s="10"/>
       <c r="C100" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13281,16 +12079,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A102" s="8"/>
+      <c r="B102" s="10"/>
       <c r="C102" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13325,16 +12115,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A104" s="8"/>
+      <c r="B104" s="10"/>
       <c r="C104" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13369,16 +12151,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A106" s="8"/>
+      <c r="B106" s="10"/>
       <c r="C106" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13413,16 +12187,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A108" s="8"/>
+      <c r="B108" s="10"/>
       <c r="C108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13457,16 +12223,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A110" s="8"/>
+      <c r="B110" s="10"/>
       <c r="C110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13501,16 +12259,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 연구개발업</t>
-        </is>
-      </c>
+      <c r="A112" s="8"/>
+      <c r="B112" s="10"/>
       <c r="C112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">82112</t>
@@ -13545,16 +12295,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
-        </is>
-      </c>
+      <c r="A114" s="8"/>
+      <c r="B114" s="10"/>
       <c r="C114" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">84202</t>
@@ -13589,16 +12331,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
+      <c r="A116" s="8"/>
+      <c r="B116" s="10"/>
       <c r="C116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">84202</t>
@@ -13633,16 +12367,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">531</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 유기성 폐자원 처리업</t>
-        </is>
-      </c>
+      <c r="A118" s="8"/>
+      <c r="B118" s="10"/>
       <c r="C118" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">89120</t>
@@ -13677,16 +12403,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 방제·농업환경 관리업</t>
-        </is>
-      </c>
+      <c r="A120" s="8"/>
+      <c r="B120" s="10"/>
       <c r="C120" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">24299</t>
@@ -13721,16 +12439,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A122" s="8"/>
+      <c r="B122" s="10"/>
       <c r="C122" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">89409</t>
@@ -13743,8 +12453,96 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="89">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="A121:A122"/>
+    <mergeCell ref="B121:B122"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13812,16 +12610,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 생산업</t>
-        </is>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">7020</t>
@@ -13922,16 +12712,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생산업</t>
-        </is>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3020</t>
@@ -13966,16 +12748,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -13988,16 +12762,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3030</t>
@@ -14010,16 +12776,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3000</t>
@@ -14032,16 +12790,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8010</t>
@@ -14076,16 +12826,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3020</t>
@@ -14098,16 +12840,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3030</t>
@@ -14120,16 +12854,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -14142,16 +12868,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8010</t>
@@ -14186,16 +12904,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A22" s="8"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3050</t>
@@ -14208,16 +12918,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A23" s="8"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -14230,16 +12932,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 유래 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A24" s="8"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8010</t>
@@ -14274,16 +12968,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A26" s="8"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3000</t>
@@ -14296,16 +12982,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 소재 제조업</t>
-        </is>
-      </c>
+      <c r="A27" s="8"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8010</t>
@@ -14406,16 +13084,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
-        </is>
-      </c>
+      <c r="A32" s="8"/>
+      <c r="B32" s="10"/>
       <c r="C32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -14428,16 +13098,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 제조업</t>
-        </is>
-      </c>
+      <c r="A33" s="8"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8010</t>
@@ -14648,16 +13310,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
-        </is>
-      </c>
+      <c r="A43" s="8"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2010</t>
@@ -14670,16 +13324,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 제조업</t>
-        </is>
-      </c>
+      <c r="A44" s="8"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -14714,16 +13360,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
+      <c r="A46" s="8"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -14736,16 +13374,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
+      <c r="A47" s="8"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">4000</t>
@@ -15044,16 +13674,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
-        </is>
-      </c>
+      <c r="A61" s="8"/>
+      <c r="B61" s="10"/>
       <c r="C61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">7020</t>
@@ -15066,16 +13688,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자 연구개발업</t>
-        </is>
-      </c>
+      <c r="A62" s="8"/>
+      <c r="B62" s="10"/>
       <c r="C62" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15110,16 +13724,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 연구개발업</t>
-        </is>
-      </c>
+      <c r="A64" s="8"/>
+      <c r="B64" s="10"/>
       <c r="C64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15154,16 +13760,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">413</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충 연구개발업</t>
-        </is>
-      </c>
+      <c r="A66" s="8"/>
+      <c r="B66" s="10"/>
       <c r="C66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15198,16 +13796,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">419</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 연구개발업</t>
-        </is>
-      </c>
+      <c r="A68" s="8"/>
+      <c r="B68" s="10"/>
       <c r="C68" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15242,16 +13832,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오농약 연구개발업</t>
-        </is>
-      </c>
+      <c r="A70" s="8"/>
+      <c r="B70" s="10"/>
       <c r="C70" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15286,16 +13868,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오비료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A72" s="8"/>
+      <c r="B72" s="10"/>
       <c r="C72" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15330,16 +13904,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">423</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바이오사료 연구개발업</t>
-        </is>
-      </c>
+      <c r="A74" s="8"/>
+      <c r="B74" s="10"/>
       <c r="C74" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15374,16 +13940,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 농자재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A76" s="8"/>
+      <c r="B76" s="10"/>
       <c r="C76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15418,16 +13976,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A78" s="8"/>
+      <c r="B78" s="10"/>
       <c r="C78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3030</t>
@@ -15440,16 +13990,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A79" s="8"/>
+      <c r="B79" s="10"/>
       <c r="C79" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3000</t>
@@ -15462,16 +14004,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">431</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 소재 연구개발업</t>
-        </is>
-      </c>
+      <c r="A80" s="8"/>
+      <c r="B80" s="10"/>
       <c r="C80" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15506,16 +14040,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A82" s="8"/>
+      <c r="B82" s="10"/>
       <c r="C82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15550,16 +14076,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">433</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
-        </is>
-      </c>
+      <c r="A84" s="8"/>
+      <c r="B84" s="10"/>
       <c r="C84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">3040</t>
@@ -15572,16 +14090,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">433</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품용 발효·미생물 기술 연구개발업</t>
-        </is>
-      </c>
+      <c r="A85" s="8"/>
+      <c r="B85" s="10"/>
       <c r="C85" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15616,16 +14126,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">434</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 대체식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A87" s="8"/>
+      <c r="B87" s="10"/>
       <c r="C87" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15660,16 +14162,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">435</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A89" s="8"/>
+      <c r="B89" s="10"/>
       <c r="C89" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15704,16 +14198,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 식품소재·식품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A91" s="8"/>
+      <c r="B91" s="10"/>
       <c r="C91" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15748,16 +14234,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">441</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 바이오 백신 연구개발업</t>
-        </is>
-      </c>
+      <c r="A93" s="8"/>
+      <c r="B93" s="10"/>
       <c r="C93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15792,16 +14270,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">449</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A95" s="8"/>
+      <c r="B95" s="10"/>
       <c r="C95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15836,16 +14306,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A97" s="8"/>
+      <c r="B97" s="10"/>
       <c r="C97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15880,16 +14342,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A99" s="8"/>
+      <c r="B99" s="10"/>
       <c r="C99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2010</t>
@@ -15902,16 +14356,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A100" s="8"/>
+      <c r="B100" s="10"/>
       <c r="C100" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">2000</t>
@@ -15924,16 +14370,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">452</t>
-        </is>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생활제품 연구개발업</t>
-        </is>
-      </c>
+      <c r="A101" s="8"/>
+      <c r="B101" s="10"/>
       <c r="C101" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -15968,16 +14406,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A103" s="8"/>
+      <c r="B103" s="10"/>
       <c r="C103" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">4030</t>
@@ -15990,16 +14420,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A104" s="8"/>
+      <c r="B104" s="10"/>
       <c r="C104" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">4000</t>
@@ -16012,16 +14434,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">461</t>
-        </is>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 환경서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A105" s="8"/>
+      <c r="B105" s="10"/>
       <c r="C105" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8040</t>
@@ -16056,16 +14470,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462</t>
-        </is>
-      </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털서비스 연구개발업</t>
-        </is>
-      </c>
+      <c r="A107" s="8"/>
+      <c r="B107" s="10"/>
       <c r="C107" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8000</t>
@@ -16122,16 +14528,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 디지털육종 서비스업</t>
-        </is>
-      </c>
+      <c r="A110" s="8"/>
+      <c r="B110" s="10"/>
       <c r="C110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8000</t>
@@ -16166,16 +14564,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">529</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 정보·데이터 서비스업</t>
-        </is>
-      </c>
+      <c r="A112" s="8"/>
+      <c r="B112" s="10"/>
       <c r="C112" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8000</t>
@@ -16254,16 +14644,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 서비스업</t>
-        </is>
-      </c>
+      <c r="A116" s="8"/>
+      <c r="B116" s="10"/>
       <c r="C116" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">8000</t>
@@ -16276,8 +14658,72 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="65">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="B77:B80"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
